--- a/data/processed/gyeongnam_high_schools_policy_feedback.xlsx
+++ b/data/processed/gyeongnam_high_schools_policy_feedback.xlsx
@@ -552,7 +552,7 @@
         <v>0.1</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -564,10 +564,10 @@
         <v>0.03333333333333333</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4333333333333333</v>
+        <v>0.4444333333333333</v>
       </c>
       <c r="M2" t="n">
-        <v>0.4</v>
+        <v>0.4111</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -601,7 +601,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>해당 학교는 상담수요지수(CDI=0.433)가 상담공급지수(CSI=0.033)보다 높아 수요 대비 공급이 상대적으로 부족한 학교로 분류된다. 우선지원점수는 0.400로, 수요가 공급보다 높은 상태이다. 특히 상담인력 공급 점수, Wee클래스 미운영, Wee센터 접근성 점수, 학교폭력 위험 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담수요지수(CDI=0.444)가 상담공급지수(CSI=0.033)보다 높아 수요 대비 공급이 상대적으로 부족한 학교로 분류된다. 우선지원점수는 0.411로, 수요가 공급보다 높은 상태이다. 특히 상담인력 공급 점수, Wee클래스 미운영, Wee센터 접근성 점수, 학교폭력 위험 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
@@ -636,7 +636,7 @@
         <v>0.1</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="I3" t="n">
         <v>0.032183814105257</v>
@@ -648,10 +648,10 @@
         <v>0.03333333333333333</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4289345541140421</v>
+        <v>0.4400345541140422</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3956012207807088</v>
+        <v>0.4067012207807089</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -685,7 +685,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>해당 학교는 상담수요지수(CDI=0.429)가 상담공급지수(CSI=0.033)보다 높아 수요 대비 공급이 상대적으로 부족한 학교로 분류된다. 우선지원점수는 0.396로, 수요가 공급보다 높은 상태이다. 특히 상담인력 공급 점수, Wee클래스 미운영, Wee센터 접근성 점수, 학교폭력 위험 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담수요지수(CDI=0.440)가 상담공급지수(CSI=0.033)보다 높아 수요 대비 공급이 상대적으로 부족한 학교로 분류된다. 우선지원점수는 0.407로, 수요가 공급보다 높은 상태이다. 특히 상담인력 공급 점수, Wee클래스 미운영, Wee센터 접근성 점수, 학교폭력 위험 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
@@ -720,7 +720,7 @@
         <v>0.1</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="I4" t="n">
         <v>0.3477738096487907</v>
@@ -732,10 +732,10 @@
         <v>0.03333333333333333</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2159246032162635</v>
+        <v>0.2270246032162636</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1825912698829302</v>
+        <v>0.1936912698829303</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -769,19 +769,19 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>해당 학교는 상담수요지수(CDI=0.216)가 상담공급지수(CSI=0.033)보다 높아 수요 대비 공급이 상대적으로 부족한 학교로 분류된다. 우선지원점수는 0.183로, 수요가 공급보다 높은 상태이다. 특히 상담인력 공급 점수, Wee클래스 미운영, Wee센터 접근성 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담수요지수(CDI=0.227)가 상담공급지수(CSI=0.033)보다 높아 수요 대비 공급이 상대적으로 부족한 학교로 분류된다. 우선지원점수는 0.194로, 수요가 공급보다 높은 상태이다. 특히 상담인력 공급 점수, Wee클래스 미운영, Wee센터 접근성 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>480041680</t>
+          <t>480041912</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>마산제일고등학교</t>
+          <t>칠원고등학교</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>창원시</t>
+          <t>함안군</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -801,25 +801,25 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0.6667</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0064036137928232</v>
+        <v>0.2179458060877966</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1275259674859008</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2333333333333333</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="L5" t="n">
-        <v>0.377976527092908</v>
+        <v>0.2948819353625988</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1446431937595747</v>
+        <v>0.1615486020292655</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -833,12 +833,12 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>수요 보통</t>
+          <t>수요 낮음</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>A. 수요높음-공급낮음</t>
+          <t>C. 수요낮음-공급낮음</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -848,12 +848,12 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>전문상담교사 배치 또는 순회상담교사 연계 검토; Wee클래스 신설 또는 운영 현황 재확인 검토; 대규모 학교로 상담수요 규모가 커 상담 인력 보강 검토; 학교폭력 피해 응답률 기반 위험 점수가 높아 학교폭력 관련 상담지원 강화 검토; 상담수요지수가 상담공급지수보다 높아 우선 지원 검토 필요</t>
+          <t>전문상담교사 배치 또는 순회상담교사 연계 검토; Wee클래스 신설 또는 운영 현황 재확인 검토; Wee센터 접근성이 낮아 이동형 상담, 온라인 상담, 권역별 연계 강화 검토; 상담수요지수가 상담공급지수보다 높아 우선 지원 검토 필요</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>해당 학교는 상담수요지수(CDI=0.378)가 상담공급지수(CSI=0.233)보다 높아 수요 대비 공급이 상대적으로 부족한 학교로 분류된다. 우선지원점수는 0.145로, 수요가 공급보다 높은 상태이다. 특히 상담인력 공급 점수, Wee클래스 미운영, 학교폭력 위험 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담수요지수(CDI=0.295)가 상담공급지수(CSI=0.133)보다 높아 수요 대비 공급이 상대적으로 부족한 학교로 분류된다. 우선지원점수는 0.162로, 수요가 공급보다 높은 상태이다. 특히 상담인력 공급 점수, Wee클래스 미운영, Wee센터 접근성 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
@@ -888,7 +888,7 @@
         <v>0.1</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="I6" t="n">
         <v>0.2283316038840079</v>
@@ -900,10 +900,10 @@
         <v>0.03333333333333333</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1761105346280026</v>
+        <v>0.1872105346280026</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1427772012946693</v>
+        <v>0.1538772012946693</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -937,19 +937,19 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>해당 학교는 상담수요지수(CDI=0.176)가 상담공급지수(CSI=0.033)보다 높아 수요 대비 공급이 상대적으로 부족한 학교로 분류된다. 우선지원점수는 0.143로, 수요가 공급보다 높은 상태이다. 특히 상담인력 공급 점수, Wee클래스 미운영, Wee센터 접근성 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담수요지수(CDI=0.187)가 상담공급지수(CSI=0.033)보다 높아 수요 대비 공급이 상대적으로 부족한 학교로 분류된다. 우선지원점수는 0.154로, 수요가 공급보다 높은 상태이다. 특히 상담인력 공급 점수, Wee클래스 미운영, Wee센터 접근성 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>480041912</t>
+          <t>480041680</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>칠원고등학교</t>
+          <t>마산제일고등학교</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>함안군</t>
+          <t>창원시</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -969,25 +969,25 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2179458060877966</v>
+        <v>0.0064036137928232</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>0.1275259674859008</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.2333333333333333</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2726486020292655</v>
+        <v>0.377976527092908</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1393152686959322</v>
+        <v>0.1446431937595747</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>수요 낮음</t>
+          <t>수요 보통</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1016,12 +1016,12 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>전문상담교사 배치 또는 순회상담교사 연계 검토; Wee클래스 신설 또는 운영 현황 재확인 검토; Wee센터 접근성이 낮아 이동형 상담, 온라인 상담, 권역별 연계 강화 검토; 상담수요지수가 상담공급지수보다 높아 우선 지원 검토 필요</t>
+          <t>전문상담교사 배치 또는 순회상담교사 연계 검토; Wee클래스 신설 또는 운영 현황 재확인 검토; 대규모 학교로 상담수요 규모가 커 상담 인력 보강 검토; 학교폭력 피해 응답률 기반 위험 점수가 높아 학교폭력 관련 상담지원 강화 검토; 상담수요지수가 상담공급지수보다 높아 우선 지원 검토 필요</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>해당 학교는 상담수요지수(CDI=0.273)가 상담공급지수(CSI=0.133)보다 높아 수요 대비 공급이 상대적으로 부족한 학교로 분류된다. 우선지원점수는 0.139로, 수요가 공급보다 높은 상태이다. 특히 상담인력 공급 점수, Wee클래스 미운영, Wee센터 접근성 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담수요지수(CDI=0.378)가 상담공급지수(CSI=0.233)보다 높아 수요 대비 공급이 상대적으로 부족한 학교로 분류된다. 우선지원점수는 0.145로, 수요가 공급보다 높은 상태이다. 특히 상담인력 공급 점수, Wee클래스 미운영, 학교폭력 위험 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
@@ -1196,12 +1196,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>480041788</t>
+          <t>480041660</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>효암고등학교</t>
+          <t>남해해성고등학교</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1211,35 +1211,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>양산시</t>
+          <t>남해군</t>
         </is>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>0.6667</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2062807374204296</v>
+        <v>0.2281883551218987</v>
       </c>
       <c r="J10" t="n">
-        <v>0.09879755922469491</v>
+        <v>0.02564102564102564</v>
       </c>
       <c r="K10" t="n">
-        <v>0.3666666666666667</v>
+        <v>0.2333333333333333</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4350260988817081</v>
+        <v>0.3068431269209748</v>
       </c>
       <c r="M10" t="n">
-        <v>0.06835943221504143</v>
+        <v>0.07350979358764151</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>공급 보통</t>
+          <t>공급 낮음</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>A. 수요높음-공급낮음</t>
+          <t>C. 수요낮음-공급낮음</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>전문상담교사 배치 또는 순회상담교사 연계 검토; Wee센터 접근성이 낮아 이동형 상담, 온라인 상담, 권역별 연계 강화 검토; 대규모 학교로 상담수요 규모가 커 상담 인력 보강 검토; 상담수요지수가 상담공급지수보다 높아 우선 지원 검토 필요</t>
+          <t>전문상담교사 배치 또는 순회상담교사 연계 검토; Wee클래스 신설 또는 운영 현황 재확인 검토; 상담수요지수가 상담공급지수보다 높아 우선 지원 검토 필요</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>해당 학교는 상담수요지수(CDI=0.435)가 상담공급지수(CSI=0.367)보다 높아 수요 대비 공급이 상대적으로 부족한 학교로 분류된다. 우선지원점수는 0.068로, 수요가 공급보다 높은 상태이다. 특히 상담인력 공급 점수, Wee센터 접근성 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담수요지수(CDI=0.307)가 상담공급지수(CSI=0.233)보다 높아 수요 대비 공급이 상대적으로 부족한 학교로 분류된다. 우선지원점수는 0.074로, 수요가 공급보다 높은 상태이다. 특히 상담인력 공급 점수, Wee클래스 미운영이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
         <v>0.1</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="I11" t="n">
         <v>0.78680479825518</v>
@@ -1320,10 +1320,10 @@
         <v>0.3666666666666667</v>
       </c>
       <c r="L11" t="n">
-        <v>0.4275264894494527</v>
+        <v>0.4386264894494527</v>
       </c>
       <c r="M11" t="n">
-        <v>0.06085982278278601</v>
+        <v>0.07195982278278601</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1357,19 +1357,19 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>해당 학교는 상담수요지수(CDI=0.428)가 상담공급지수(CSI=0.367)보다 높아 수요 대비 공급이 상대적으로 부족한 학교로 분류된다. 우선지원점수는 0.061로, 수요가 공급보다 높은 상태이다. 특히 상담인력 공급 점수, Wee센터 접근성 점수, 학교폭력 위험 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담수요지수(CDI=0.439)가 상담공급지수(CSI=0.367)보다 높아 수요 대비 공급이 상대적으로 부족한 학교로 분류된다. 우선지원점수는 0.072로, 수요가 공급보다 높은 상태이다. 특히 상담인력 공급 점수, Wee센터 접근성 점수, 학교폭력 위험 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>480041660</t>
+          <t>480041788</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>남해해성고등학교</t>
+          <t>효암고등학교</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1379,35 +1379,35 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>남해군</t>
+          <t>양산시</t>
         </is>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2281883551218987</v>
+        <v>0.2062807374204296</v>
       </c>
       <c r="J12" t="n">
-        <v>0.02564102564102564</v>
+        <v>0.09879755922469491</v>
       </c>
       <c r="K12" t="n">
-        <v>0.2333333333333333</v>
+        <v>0.3666666666666667</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2846097935876414</v>
+        <v>0.4350260988817081</v>
       </c>
       <c r="M12" t="n">
-        <v>0.05127646025430807</v>
+        <v>0.06835943221504143</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1416,17 +1416,17 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>공급 낮음</t>
+          <t>공급 보통</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>수요 낮음</t>
+          <t>수요 보통</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>C. 수요낮음-공급낮음</t>
+          <t>A. 수요높음-공급낮음</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1436,12 +1436,12 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>전문상담교사 배치 또는 순회상담교사 연계 검토; Wee클래스 신설 또는 운영 현황 재확인 검토; 상담수요지수가 상담공급지수보다 높아 우선 지원 검토 필요</t>
+          <t>전문상담교사 배치 또는 순회상담교사 연계 검토; Wee센터 접근성이 낮아 이동형 상담, 온라인 상담, 권역별 연계 강화 검토; 대규모 학교로 상담수요 규모가 커 상담 인력 보강 검토; 상담수요지수가 상담공급지수보다 높아 우선 지원 검토 필요</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>해당 학교는 상담수요지수(CDI=0.285)가 상담공급지수(CSI=0.233)보다 높아 수요 대비 공급이 상대적으로 부족한 학교로 분류된다. 우선지원점수는 0.051로, 수요가 공급보다 높은 상태이다. 특히 상담인력 공급 점수, Wee클래스 미운영이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담수요지수(CDI=0.435)가 상담공급지수(CSI=0.367)보다 높아 수요 대비 공급이 상대적으로 부족한 학교로 분류된다. 우선지원점수는 0.068로, 수요가 공급보다 높은 상태이다. 특히 상담인력 공급 점수, Wee센터 접근성 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
@@ -1476,7 +1476,7 @@
         <v>0.4</v>
       </c>
       <c r="H13" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="I13" t="n">
         <v>0.2006693383532846</v>
@@ -1488,10 +1488,10 @@
         <v>0.1333333333333333</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1668897794510948</v>
+        <v>0.1779897794510949</v>
       </c>
       <c r="M13" t="n">
-        <v>0.03355644611776148</v>
+        <v>0.04465644611776159</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>해당 학교는 상담수요지수(CDI=0.167)가 상담공급지수(CSI=0.133)보다 높아 수요 대비 공급이 상대적으로 부족한 학교로 분류된다. 우선지원점수는 0.034로, 수요가 공급보다 높은 상태이다. 특히 상담인력 공급 점수, Wee클래스 미운영, Wee센터 접근성 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담수요지수(CDI=0.178)가 상담공급지수(CSI=0.133)보다 높아 수요 대비 공급이 상대적으로 부족한 학교로 분류된다. 우선지원점수는 0.045로, 수요가 공급보다 높은 상태이다. 특히 상담인력 공급 점수, Wee클래스 미운영, Wee센터 접근성 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
@@ -1812,7 +1812,7 @@
         <v>0.4</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="I17" t="n">
         <v>0.0108114159662646</v>
@@ -1824,10 +1824,10 @@
         <v>0.1333333333333333</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1036038053220882</v>
+        <v>0.1147038053220882</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.02972952801124511</v>
+        <v>-0.01862952801124511</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.133)가 상담수요지수(CDI=0.104)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.030로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수, Wee클래스 미운영, Wee센터 접근성 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.133)가 상담수요지수(CDI=0.115)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.019로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수, Wee클래스 미운영, Wee센터 접근성 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
@@ -2148,7 +2148,7 @@
         <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="I21" t="n">
         <v>0.020796896772864</v>
@@ -2160,10 +2160,10 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="L21" t="n">
-        <v>0.2309249201268014</v>
+        <v>0.2531582534601347</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.1024084132065319</v>
+        <v>-0.08017507987319861</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -2197,19 +2197,19 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.333)가 상담수요지수(CDI=0.231)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.102로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수, Wee클래스 미운영이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.333)가 상담수요지수(CDI=0.253)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.080로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수, Wee클래스 미운영이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>480041415</t>
+          <t>480041515</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>웅상고등학교</t>
+          <t>창원성민여자고등학교</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2219,35 +2219,35 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>양산시</t>
+          <t>창원시</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>0.6667</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3533756980719273</v>
+        <v>0.0083591781576696</v>
       </c>
       <c r="J22" t="n">
-        <v>0.1186373547998291</v>
+        <v>0.03989642247994184</v>
       </c>
       <c r="K22" t="n">
-        <v>0.6</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L22" t="n">
-        <v>0.4906710176239188</v>
+        <v>0.2383185335458705</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.1093289823760812</v>
+        <v>-0.09501479978746283</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -2256,17 +2256,17 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>공급 양호</t>
+          <t>공급 보통</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>수요 보통</t>
+          <t>수요 낮음</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>A. 수요높음-공급낮음</t>
+          <t>C. 수요낮음-공급낮음</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2276,24 +2276,24 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>Wee센터 접근성이 낮아 이동형 상담, 온라인 상담, 권역별 연계 강화 검토; 대규모 학교로 상담수요 규모가 커 상담 인력 보강 검토; 학교폭력 피해 응답률 기반 위험 점수가 높아 학교폭력 관련 상담지원 강화 검토</t>
+          <t>전문상담교사 배치 또는 순회상담교사 연계 검토; Wee클래스 신설 또는 운영 현황 재확인 검토</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.600)가 상담수요지수(CDI=0.491)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.109로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 Wee센터 접근성 점수, 학교폭력 위험 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.333)가 상담수요지수(CDI=0.238)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.095로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수, Wee클래스 미운영이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>480041515</t>
+          <t>480041937</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>창원성민여자고등학교</t>
+          <t>창녕옥야고등학교</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2303,35 +2303,35 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>창원시</t>
+          <t>창녕군</t>
         </is>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="H23" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0083591781576696</v>
+        <v>0.2314199132474892</v>
       </c>
       <c r="J23" t="n">
-        <v>0.03989642247994184</v>
+        <v>0.1838490566037736</v>
       </c>
       <c r="K23" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4666666666666666</v>
       </c>
       <c r="L23" t="n">
-        <v>0.2160852002125372</v>
+        <v>0.3606563232837542</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.1172481331207961</v>
+        <v>-0.1060103433829124</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>수요 낮음</t>
+          <t>수요 보통</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -2360,24 +2360,24 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>전문상담교사 배치 또는 순회상담교사 연계 검토; Wee클래스 신설 또는 운영 현황 재확인 검토</t>
+          <t>전문상담교사 배치 또는 순회상담교사 연계 검토; Wee센터 접근성이 낮아 이동형 상담, 온라인 상담, 권역별 연계 강화 검토; 학교폭력 피해 응답률 기반 위험 점수가 높아 학교폭력 관련 상담지원 강화 검토</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.333)가 상담수요지수(CDI=0.216)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.117로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수, Wee클래스 미운영이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.467)가 상담수요지수(CDI=0.361)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.106로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수, Wee센터 접근성 점수, 학교폭력 위험 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>480041175</t>
+          <t>480041415</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>김해가야고등학교</t>
+          <t>웅상고등학교</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2387,35 +2387,35 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>김해시</t>
+          <t>양산시</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="F24" t="n">
         <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="H24" t="n">
         <v>1</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4928247358275297</v>
+        <v>0.3533756980719273</v>
       </c>
       <c r="J24" t="n">
-        <v>0.1490343736403845</v>
+        <v>0.1186373547998291</v>
       </c>
       <c r="K24" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6</v>
       </c>
       <c r="L24" t="n">
-        <v>0.5472863698226381</v>
+        <v>0.4906710176239188</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.1193802968440285</v>
+        <v>-0.1093289823760812</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>B. 수요높음-공급높음</t>
+          <t>A. 수요높음-공급낮음</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2444,24 +2444,24 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>전문상담교사 배치 또는 순회상담교사 연계 검토; 대규모 학교로 상담수요 규모가 커 상담 인력 보강 검토; 실제 상담 이용 수준이 높아 상담 프로그램 확대 또는 상담 인력 보완 검토; 학교폭력 피해 응답률 기반 위험 점수가 높아 학교폭력 관련 상담지원 강화 검토</t>
+          <t>Wee센터 접근성이 낮아 이동형 상담, 온라인 상담, 권역별 연계 강화 검토; 대규모 학교로 상담수요 규모가 커 상담 인력 보강 검토; 학교폭력 피해 응답률 기반 위험 점수가 높아 학교폭력 관련 상담지원 강화 검토</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.547)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.119로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수, 학교폭력 위험 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.600)가 상담수요지수(CDI=0.491)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.109로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 Wee센터 접근성 점수, 학교폭력 위험 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>480041460</t>
+          <t>480041612</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>진해고등학교</t>
+          <t>거창고등학교</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2471,35 +2471,35 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>창원시</t>
+          <t>거창군</t>
         </is>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>0.6667</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2271658647607984</v>
+        <v>0.0011011854958523</v>
       </c>
       <c r="J25" t="n">
-        <v>0.1062570197451786</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>0.5666666666666667</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L25" t="n">
-        <v>0.4444742948353257</v>
+        <v>0.2226003951652841</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.122192371831341</v>
+        <v>-0.1107329381680492</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -2513,12 +2513,12 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>수요 보통</t>
+          <t>수요 낮음</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>A. 수요높음-공급낮음</t>
+          <t>C. 수요낮음-공급낮음</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -2528,24 +2528,24 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>전문상담교사 배치 또는 순회상담교사 연계 검토; 대규모 학교로 상담수요 규모가 커 상담 인력 보강 검토</t>
+          <t>전문상담교사 배치 또는 순회상담교사 연계 검토; Wee클래스 신설 또는 운영 현황 재확인 검토</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.567)가 상담수요지수(CDI=0.444)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.122로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.333)가 상담수요지수(CDI=0.223)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.111로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수, Wee클래스 미운영이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>480041937</t>
+          <t>480041708</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>창녕옥야고등학교</t>
+          <t>보광고등학교</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2555,35 +2555,35 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>창녕군</t>
+          <t>양산시</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="F26" t="n">
         <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="H26" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.5952075874026673</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.1930397432721377</v>
+      </c>
+      <c r="K26" t="n">
         <v>0.6</v>
       </c>
-      <c r="I26" t="n">
-        <v>0.2314199132474892</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0.1838490566037736</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0.4666666666666666</v>
-      </c>
       <c r="L26" t="n">
-        <v>0.3384229899504209</v>
+        <v>0.4849824435582684</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.1282436767162457</v>
+        <v>-0.1150175564417316</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>공급 보통</t>
+          <t>공급 양호</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -2602,7 +2602,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>C. 수요낮음-공급낮음</t>
+          <t>A. 수요높음-공급낮음</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -2612,24 +2612,24 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>전문상담교사 배치 또는 순회상담교사 연계 검토; Wee센터 접근성이 낮아 이동형 상담, 온라인 상담, 권역별 연계 강화 검토; 학교폭력 피해 응답률 기반 위험 점수가 높아 학교폭력 관련 상담지원 강화 검토</t>
+          <t>Wee센터 접근성이 낮아 이동형 상담, 온라인 상담, 권역별 연계 강화 검토; 실제 상담 이용 수준이 높아 상담 프로그램 확대 또는 상담 인력 보완 검토; 학교폭력 피해 응답률 기반 위험 점수가 높아 학교폭력 관련 상담지원 강화 검토</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.467)가 상담수요지수(CDI=0.338)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.128로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수, Wee센터 접근성 점수, 학교폭력 위험 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.600)가 상담수요지수(CDI=0.485)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.115로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 Wee센터 접근성 점수, 학교폭력 위험 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>480041520</t>
+          <t>480041175</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>통영여자고등학교</t>
+          <t>김해가야고등학교</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>통영시</t>
+          <t>김해시</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -2655,19 +2655,19 @@
         <v>1</v>
       </c>
       <c r="I27" t="n">
-        <v>0.5158423179000511</v>
+        <v>0.4928247358275297</v>
       </c>
       <c r="J27" t="n">
-        <v>0.09815651617954205</v>
+        <v>0.1490343736403845</v>
       </c>
       <c r="K27" t="n">
         <v>0.6666666666666666</v>
       </c>
       <c r="L27" t="n">
-        <v>0.5379996113598644</v>
+        <v>0.5472863698226381</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.1286670553068022</v>
+        <v>-0.1193802968440285</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -2696,24 +2696,24 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>전문상담교사 배치 또는 순회상담교사 연계 검토; 대규모 학교로 상담수요 규모가 커 상담 인력 보강 검토; 실제 상담 이용 수준이 높아 상담 프로그램 확대 또는 상담 인력 보완 검토</t>
+          <t>전문상담교사 배치 또는 순회상담교사 연계 검토; 대규모 학교로 상담수요 규모가 커 상담 인력 보강 검토; 실제 상담 이용 수준이 높아 상담 프로그램 확대 또는 상담 인력 보완 검토; 학교폭력 피해 응답률 기반 위험 점수가 높아 학교폭력 관련 상담지원 강화 검토</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.538)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.129로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.547)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.119로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수, 학교폭력 위험 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>480041612</t>
+          <t>480041460</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>거창고등학교</t>
+          <t>진해고등학교</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2723,35 +2723,35 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>거창군</t>
+          <t>창원시</t>
         </is>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G28" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="H28" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="I28" t="n">
-        <v>0.0011011854958523</v>
+        <v>0.2271658647607984</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>0.1062570197451786</v>
       </c>
       <c r="K28" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="L28" t="n">
-        <v>0.2003670618319507</v>
+        <v>0.4444742948353257</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.1329662715013826</v>
+        <v>-0.122192371831341</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -2765,12 +2765,12 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>수요 낮음</t>
+          <t>수요 보통</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>C. 수요낮음-공급낮음</t>
+          <t>A. 수요높음-공급낮음</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -2780,24 +2780,24 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>전문상담교사 배치 또는 순회상담교사 연계 검토; Wee클래스 신설 또는 운영 현황 재확인 검토</t>
+          <t>전문상담교사 배치 또는 순회상담교사 연계 검토; 대규모 학교로 상담수요 규모가 커 상담 인력 보강 검토</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.333)가 상담수요지수(CDI=0.200)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.133로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수, Wee클래스 미운영이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.567)가 상담수요지수(CDI=0.444)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.122로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>480041430</t>
+          <t>480041798</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>진양고등학교</t>
+          <t>용남고등학교</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>진주시</t>
+          <t>사천시</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -2817,25 +2817,25 @@
         <v>1</v>
       </c>
       <c r="G29" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="H29" t="n">
-        <v>1</v>
+        <v>0.6667</v>
       </c>
       <c r="I29" t="n">
-        <v>0.2127050585131158</v>
+        <v>0.3138411838772603</v>
       </c>
       <c r="J29" t="n">
-        <v>0.0772717592246427</v>
+        <v>0.04618335628565808</v>
       </c>
       <c r="K29" t="n">
-        <v>0.5666666666666667</v>
+        <v>0.4666666666666666</v>
       </c>
       <c r="L29" t="n">
-        <v>0.4299922725792529</v>
+        <v>0.3422415133876395</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.1366743940874138</v>
+        <v>-0.1244251532790271</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
@@ -2854,7 +2854,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>A. 수요높음-공급낮음</t>
+          <t>C. 수요낮음-공급낮음</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -2864,24 +2864,24 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>전문상담교사 배치 또는 순회상담교사 연계 검토; 대규모 학교로 상담수요 규모가 커 상담 인력 보강 검토</t>
+          <t>전문상담교사 배치 또는 순회상담교사 연계 검토; Wee센터 접근성이 낮아 이동형 상담, 온라인 상담, 권역별 연계 강화 검토</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.567)가 상담수요지수(CDI=0.430)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.137로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.467)가 상담수요지수(CDI=0.342)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.124로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수, Wee센터 접근성 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>480041708</t>
+          <t>480041520</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>보광고등학교</t>
+          <t>통영여자고등학교</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2891,35 +2891,35 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>양산시</t>
+          <t>통영시</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
         <v>1</v>
       </c>
       <c r="G30" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="H30" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="I30" t="n">
-        <v>0.5952075874026673</v>
+        <v>0.5158423179000511</v>
       </c>
       <c r="J30" t="n">
-        <v>0.1930397432721377</v>
+        <v>0.09815651617954205</v>
       </c>
       <c r="K30" t="n">
-        <v>0.6</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="L30" t="n">
-        <v>0.462749110224935</v>
+        <v>0.5379996113598644</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.137250889775065</v>
+        <v>-0.1286670553068022</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>A. 수요높음-공급낮음</t>
+          <t>B. 수요높음-공급높음</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -2948,24 +2948,24 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>Wee센터 접근성이 낮아 이동형 상담, 온라인 상담, 권역별 연계 강화 검토; 실제 상담 이용 수준이 높아 상담 프로그램 확대 또는 상담 인력 보완 검토; 학교폭력 피해 응답률 기반 위험 점수가 높아 학교폭력 관련 상담지원 강화 검토</t>
+          <t>전문상담교사 배치 또는 순회상담교사 연계 검토; 대규모 학교로 상담수요 규모가 커 상담 인력 보강 검토; 실제 상담 이용 수준이 높아 상담 프로그램 확대 또는 상담 인력 보완 검토</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.600)가 상담수요지수(CDI=0.463)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.137로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 Wee센터 접근성 점수, 학교폭력 위험 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.538)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.129로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>480041684</t>
+          <t>480041891</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>마산제일여자고등학교</t>
+          <t>창원대산고등학교</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2985,25 +2985,25 @@
         <v>1</v>
       </c>
       <c r="G31" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="H31" t="n">
-        <v>1</v>
+        <v>0.6667</v>
       </c>
       <c r="I31" t="n">
-        <v>0.2113677737788978</v>
+        <v>0.2149093505434027</v>
       </c>
       <c r="J31" t="n">
-        <v>0.06897355576600861</v>
+        <v>0.1225239661720482</v>
       </c>
       <c r="K31" t="n">
-        <v>0.5666666666666667</v>
+        <v>0.4666666666666666</v>
       </c>
       <c r="L31" t="n">
-        <v>0.4267804431816355</v>
+        <v>0.3347111055718169</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.1398862234850312</v>
+        <v>-0.1319555610948497</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
@@ -3022,34 +3022,34 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>A. 수요높음-공급낮음</t>
+          <t>C. 수요낮음-공급낮음</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>수요-공급 불균형 우선 개선</t>
+          <t>권역별 순회상담 또는 최소 인프라 보완</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>전문상담교사 배치 또는 순회상담교사 연계 검토; 대규모 학교로 상담수요 규모가 커 상담 인력 보강 검토</t>
+          <t>전문상담교사 배치 또는 순회상담교사 연계 검토; Wee센터 접근성이 낮아 이동형 상담, 온라인 상담, 권역별 연계 강화 검토; 학교폭력 피해 응답률 기반 위험 점수가 높아 학교폭력 관련 상담지원 강화 검토</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.567)가 상담수요지수(CDI=0.427)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.140로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.467)가 상담수요지수(CDI=0.335)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.132로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수, Wee센터 접근성 점수, 학교폭력 위험 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>480041958</t>
+          <t>480041430</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>김해수남고등학교</t>
+          <t>진양고등학교</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3059,35 +3059,35 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>김해시</t>
+          <t>진주시</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
         <v>1</v>
       </c>
       <c r="G32" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="H32" t="n">
         <v>1</v>
       </c>
       <c r="I32" t="n">
-        <v>0.296344990720316</v>
+        <v>0.2127050585131158</v>
       </c>
       <c r="J32" t="n">
-        <v>0.07370330671481247</v>
+        <v>0.0772717592246427</v>
       </c>
       <c r="K32" t="n">
-        <v>0.6</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="L32" t="n">
-        <v>0.4566827658117095</v>
+        <v>0.4299922725792529</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.1433172341882905</v>
+        <v>-0.1366743940874138</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>공급 양호</t>
+          <t>공급 보통</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3116,24 +3116,24 @@
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>Wee센터 접근성이 낮아 이동형 상담, 온라인 상담, 권역별 연계 강화 검토; 대규모 학교로 상담수요 규모가 커 상담 인력 보강 검토</t>
+          <t>전문상담교사 배치 또는 순회상담교사 연계 검토; 대규모 학교로 상담수요 규모가 커 상담 인력 보강 검토</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.600)가 상담수요지수(CDI=0.457)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.143로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 Wee센터 접근성 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.567)가 상담수요지수(CDI=0.430)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.137로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>480041798</t>
+          <t>480041300</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>용남고등학교</t>
+          <t>삼가고등학교</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3143,35 +3143,35 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>사천시</t>
+          <t>합천군</t>
         </is>
       </c>
       <c r="E33" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" t="n">
         <v>0</v>
       </c>
-      <c r="F33" t="n">
-        <v>1</v>
-      </c>
       <c r="G33" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="H33" t="n">
-        <v>0.6</v>
+        <v>0.3333</v>
       </c>
       <c r="I33" t="n">
-        <v>0.3138411838772603</v>
+        <v>0.1721507225361336</v>
       </c>
       <c r="J33" t="n">
-        <v>0.04618335628565808</v>
+        <v>0.1818181818181819</v>
       </c>
       <c r="K33" t="n">
-        <v>0.4666666666666666</v>
+        <v>0.3666666666666667</v>
       </c>
       <c r="L33" t="n">
-        <v>0.3200081800543061</v>
+        <v>0.2290896347847718</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.1466584866123605</v>
+        <v>-0.1375770318818949</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
@@ -3185,7 +3185,7 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>수요 보통</t>
+          <t>수요 낮음</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
@@ -3200,24 +3200,24 @@
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>전문상담교사 배치 또는 순회상담교사 연계 검토; Wee센터 접근성이 낮아 이동형 상담, 온라인 상담, 권역별 연계 강화 검토</t>
+          <t>Wee클래스 신설 또는 운영 현황 재확인 검토; Wee센터 접근성이 낮아 이동형 상담, 온라인 상담, 권역별 연계 강화 검토; 학교폭력 피해 응답률 기반 위험 점수가 높아 학교폭력 관련 상담지원 강화 검토</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.467)가 상담수요지수(CDI=0.320)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.147로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수, Wee센터 접근성 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.367)가 상담수요지수(CDI=0.229)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.138로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 Wee클래스 미운영, Wee센터 접근성 점수, 학교폭력 위험 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>480041300</t>
+          <t>480041684</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>삼가고등학교</t>
+          <t>마산제일여자고등학교</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3227,35 +3227,35 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>합천군</t>
+          <t>창원시</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G34" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="H34" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1721507225361336</v>
+        <v>0.2113677737788978</v>
       </c>
       <c r="J34" t="n">
-        <v>0.1818181818181819</v>
+        <v>0.06897355576600861</v>
       </c>
       <c r="K34" t="n">
-        <v>0.3666666666666667</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="L34" t="n">
-        <v>0.2179896347847718</v>
+        <v>0.4267804431816355</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.1486770318818949</v>
+        <v>-0.1398862234850312</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
@@ -3269,39 +3269,39 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>수요 낮음</t>
+          <t>수요 보통</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>C. 수요낮음-공급낮음</t>
+          <t>A. 수요높음-공급낮음</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>권역별 순회상담 또는 최소 인프라 보완</t>
+          <t>수요-공급 불균형 우선 개선</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>Wee클래스 신설 또는 운영 현황 재확인 검토; Wee센터 접근성이 낮아 이동형 상담, 온라인 상담, 권역별 연계 강화 검토; 학교폭력 피해 응답률 기반 위험 점수가 높아 학교폭력 관련 상담지원 강화 검토</t>
+          <t>전문상담교사 배치 또는 순회상담교사 연계 검토; 대규모 학교로 상담수요 규모가 커 상담 인력 보강 검토</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.367)가 상담수요지수(CDI=0.218)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.149로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 Wee클래스 미운영, Wee센터 접근성 점수, 학교폭력 위험 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.567)가 상담수요지수(CDI=0.427)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.140로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>480041930</t>
+          <t>480041958</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>거제제일고등학교</t>
+          <t>김해수남고등학교</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -3311,35 +3311,35 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>거제시</t>
+          <t>김해시</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="F35" t="n">
         <v>1</v>
       </c>
       <c r="G35" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="H35" t="n">
         <v>1</v>
       </c>
       <c r="I35" t="n">
-        <v>0.4665608525420596</v>
+        <v>0.296344990720316</v>
       </c>
       <c r="J35" t="n">
-        <v>0.0829255051656457</v>
+        <v>0.07370330671481247</v>
       </c>
       <c r="K35" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6</v>
       </c>
       <c r="L35" t="n">
-        <v>0.516495452569235</v>
+        <v>0.4566827658117095</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.1501712140974316</v>
+        <v>-0.1433172341882905</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
@@ -3358,34 +3358,34 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>B. 수요높음-공급높음</t>
+          <t>A. 수요높음-공급낮음</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>고수요 학교 모니터링 및 프로그램 강화</t>
+          <t>수요-공급 불균형 우선 개선</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>전문상담교사 배치 또는 순회상담교사 연계 검토; 대규모 학교로 상담수요 규모가 커 상담 인력 보강 검토; 실제 상담 이용 수준이 높아 상담 프로그램 확대 또는 상담 인력 보완 검토</t>
+          <t>Wee센터 접근성이 낮아 이동형 상담, 온라인 상담, 권역별 연계 강화 검토; 대규모 학교로 상담수요 규모가 커 상담 인력 보강 검토</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.516)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.150로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.600)가 상담수요지수(CDI=0.457)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.143로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 Wee센터 접근성 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>480041891</t>
+          <t>480041930</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>창원대산고등학교</t>
+          <t>거제제일고등학교</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3395,7 +3395,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>창원시</t>
+          <t>거제시</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -3405,25 +3405,25 @@
         <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="H36" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="I36" t="n">
-        <v>0.2149093505434027</v>
+        <v>0.4665608525420596</v>
       </c>
       <c r="J36" t="n">
-        <v>0.1225239661720482</v>
+        <v>0.0829255051656457</v>
       </c>
       <c r="K36" t="n">
-        <v>0.4666666666666666</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="L36" t="n">
-        <v>0.3124777722384836</v>
+        <v>0.516495452569235</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.154188894428183</v>
+        <v>-0.1501712140974316</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>공급 보통</t>
+          <t>공급 양호</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -3442,22 +3442,22 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>C. 수요낮음-공급낮음</t>
+          <t>B. 수요높음-공급높음</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>권역별 순회상담 또는 최소 인프라 보완</t>
+          <t>고수요 학교 모니터링 및 프로그램 강화</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>전문상담교사 배치 또는 순회상담교사 연계 검토; Wee센터 접근성이 낮아 이동형 상담, 온라인 상담, 권역별 연계 강화 검토; 학교폭력 피해 응답률 기반 위험 점수가 높아 학교폭력 관련 상담지원 강화 검토</t>
+          <t>전문상담교사 배치 또는 순회상담교사 연계 검토; 대규모 학교로 상담수요 규모가 커 상담 인력 보강 검토; 실제 상담 이용 수준이 높아 상담 프로그램 확대 또는 상담 인력 보완 검토</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.467)가 상담수요지수(CDI=0.312)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.154로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수, Wee센터 접근성 점수, 학교폭력 위험 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.516)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.150로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
@@ -3632,12 +3632,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>480041340</t>
+          <t>480041888</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>야로고등학교</t>
+          <t>창원남고등학교</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3647,35 +3647,35 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>합천군</t>
+          <t>창원시</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G39" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="H39" t="n">
-        <v>0.3</v>
+        <v>0.6667</v>
       </c>
       <c r="I39" t="n">
-        <v>0.2533219031874272</v>
+        <v>0.7795999680122426</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>0.05377528981354961</v>
       </c>
       <c r="K39" t="n">
-        <v>0.3666666666666667</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="L39" t="n">
-        <v>0.1844406343958091</v>
+        <v>0.5000250859419307</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.1822260322708576</v>
+        <v>-0.1666415807247359</v>
       </c>
       <c r="N39" t="inlineStr">
         <is>
@@ -3684,44 +3684,44 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>공급 보통</t>
+          <t>공급 양호</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>수요 낮음</t>
+          <t>수요 보통</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>C. 수요낮음-공급낮음</t>
+          <t>B. 수요높음-공급높음</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>권역별 순회상담 또는 최소 인프라 보완</t>
+          <t>고수요 학교 모니터링 및 프로그램 강화</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>Wee클래스 신설 또는 운영 현황 재확인 검토; Wee센터 접근성이 낮아 이동형 상담, 온라인 상담, 권역별 연계 강화 검토</t>
+          <t>전문상담교사 배치 또는 순회상담교사 연계 검토; 실제 상담 이용 수준이 높아 상담 프로그램 확대 또는 상담 인력 보완 검토</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.367)가 상담수요지수(CDI=0.184)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.182로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 Wee클래스 미운영, Wee센터 접근성 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.500)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.167로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>480041347</t>
+          <t>480041340</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>김해제일고등학교</t>
+          <t>야로고등학교</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3731,35 +3731,35 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>김해시</t>
+          <t>합천군</t>
         </is>
       </c>
       <c r="E40" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" t="n">
         <v>0</v>
       </c>
-      <c r="F40" t="n">
-        <v>1</v>
-      </c>
       <c r="G40" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="H40" t="n">
-        <v>1</v>
+        <v>0.3333</v>
       </c>
       <c r="I40" t="n">
-        <v>0.2969432680024733</v>
+        <v>0.2533219031874272</v>
       </c>
       <c r="J40" t="n">
-        <v>0.1478483958194806</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.3666666666666667</v>
       </c>
       <c r="L40" t="n">
-        <v>0.4815972212739846</v>
+        <v>0.195540634395809</v>
       </c>
       <c r="M40" t="n">
-        <v>-0.1850694453926821</v>
+        <v>-0.1711260322708577</v>
       </c>
       <c r="N40" t="inlineStr">
         <is>
@@ -3768,44 +3768,44 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>공급 양호</t>
+          <t>공급 보통</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>수요 보통</t>
+          <t>수요 낮음</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>B. 수요높음-공급높음</t>
+          <t>C. 수요낮음-공급낮음</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>고수요 학교 모니터링 및 프로그램 강화</t>
+          <t>권역별 순회상담 또는 최소 인프라 보완</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>전문상담교사 배치 또는 순회상담교사 연계 검토; 대규모 학교로 상담수요 규모가 커 상담 인력 보강 검토; 학교폭력 피해 응답률 기반 위험 점수가 높아 학교폭력 관련 상담지원 강화 검토</t>
+          <t>Wee클래스 신설 또는 운영 현황 재확인 검토; Wee센터 접근성이 낮아 이동형 상담, 온라인 상담, 권역별 연계 강화 검토</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.482)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.185로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수, 학교폭력 위험 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.367)가 상담수요지수(CDI=0.196)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.171로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 Wee클래스 미운영, Wee센터 접근성 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>480041888</t>
+          <t>480041347</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>창원남고등학교</t>
+          <t>김해제일고등학교</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3815,7 +3815,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>창원시</t>
+          <t>김해시</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -3828,22 +3828,22 @@
         <v>1</v>
       </c>
       <c r="H41" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="I41" t="n">
-        <v>0.7795999680122426</v>
+        <v>0.2969432680024733</v>
       </c>
       <c r="J41" t="n">
-        <v>0.05377528981354961</v>
+        <v>0.1478483958194806</v>
       </c>
       <c r="K41" t="n">
         <v>0.6666666666666666</v>
       </c>
       <c r="L41" t="n">
-        <v>0.4777917526085974</v>
+        <v>0.4815972212739846</v>
       </c>
       <c r="M41" t="n">
-        <v>-0.1888749140580692</v>
+        <v>-0.1850694453926821</v>
       </c>
       <c r="N41" t="inlineStr">
         <is>
@@ -3872,12 +3872,12 @@
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>전문상담교사 배치 또는 순회상담교사 연계 검토; 실제 상담 이용 수준이 높아 상담 프로그램 확대 또는 상담 인력 보완 검토</t>
+          <t>전문상담교사 배치 또는 순회상담교사 연계 검토; 대규모 학교로 상담수요 규모가 커 상담 인력 보강 검토; 학교폭력 피해 응답률 기반 위험 점수가 높아 학교폭력 관련 상담지원 강화 검토</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.478)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.189로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.482)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.185로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수, 학교폭력 위험 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
@@ -3912,7 +3912,7 @@
         <v>1</v>
       </c>
       <c r="H42" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -3924,10 +3924,10 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="L42" t="n">
-        <v>0.1340136054421769</v>
+        <v>0.1451136054421769</v>
       </c>
       <c r="M42" t="n">
-        <v>-0.1993197278911564</v>
+        <v>-0.1882197278911564</v>
       </c>
       <c r="N42" t="inlineStr">
         <is>
@@ -3961,7 +3961,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.333)가 상담수요지수(CDI=0.134)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.199로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수, Wee클래스 미운영이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.333)가 상담수요지수(CDI=0.145)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.188로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수, Wee클래스 미운영이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
@@ -3996,7 +3996,7 @@
         <v>0.4</v>
       </c>
       <c r="H43" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="I43" t="n">
         <v>0.4096972760817491</v>
@@ -4008,10 +4008,10 @@
         <v>0.4666666666666666</v>
       </c>
       <c r="L43" t="n">
-        <v>0.2657045146747776</v>
+        <v>0.2768045146747776</v>
       </c>
       <c r="M43" t="n">
-        <v>-0.200962151991889</v>
+        <v>-0.189862151991889</v>
       </c>
       <c r="N43" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.467)가 상담수요지수(CDI=0.266)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.201로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수, Wee센터 접근성 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.467)가 상담수요지수(CDI=0.277)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.190로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수, Wee센터 접근성 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
         <v>0.4</v>
       </c>
       <c r="H44" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="I44" t="n">
         <v>0.4205334769382167</v>
@@ -4092,10 +4092,10 @@
         <v>0.4666666666666666</v>
       </c>
       <c r="L44" t="n">
-        <v>0.2642742111882409</v>
+        <v>0.2753742111882409</v>
       </c>
       <c r="M44" t="n">
-        <v>-0.2023924554784257</v>
+        <v>-0.1912924554784257</v>
       </c>
       <c r="N44" t="inlineStr">
         <is>
@@ -4129,19 +4129,19 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.467)가 상담수요지수(CDI=0.264)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.202로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수, Wee센터 접근성 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.467)가 상담수요지수(CDI=0.275)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.191로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수, Wee센터 접근성 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>480041496</t>
+          <t>480041720</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>웅천고등학교</t>
+          <t>삼랑진고등학교</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -4151,11 +4151,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>창원시</t>
+          <t>밀양시</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
         <v>1</v>
@@ -4164,22 +4164,22 @@
         <v>0.4</v>
       </c>
       <c r="H45" t="n">
-        <v>1</v>
+        <v>0.3333</v>
       </c>
       <c r="I45" t="n">
-        <v>0.1791911099361308</v>
+        <v>0.3357113788902203</v>
       </c>
       <c r="J45" t="n">
-        <v>0.01284796573875803</v>
+        <v>0.1458298191869671</v>
       </c>
       <c r="K45" t="n">
-        <v>0.6</v>
+        <v>0.4666666666666666</v>
       </c>
       <c r="L45" t="n">
-        <v>0.3973463585582963</v>
+        <v>0.2716137326923958</v>
       </c>
       <c r="M45" t="n">
-        <v>-0.2026536414417037</v>
+        <v>-0.1950529339742708</v>
       </c>
       <c r="N45" t="inlineStr">
         <is>
@@ -4188,44 +4188,44 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>공급 양호</t>
+          <t>공급 보통</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>수요 보통</t>
+          <t>수요 낮음</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>A. 수요높음-공급낮음</t>
+          <t>C. 수요낮음-공급낮음</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>수요-공급 불균형 우선 개선</t>
+          <t>권역별 순회상담 또는 최소 인프라 보완</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>Wee센터 접근성이 낮아 이동형 상담, 온라인 상담, 권역별 연계 강화 검토; 대규모 학교로 상담수요 규모가 커 상담 인력 보강 검토</t>
+          <t>전문상담교사 배치 또는 순회상담교사 연계 검토; Wee센터 접근성이 낮아 이동형 상담, 온라인 상담, 권역별 연계 강화 검토; 학교폭력 피해 응답률 기반 위험 점수가 높아 학교폭력 관련 상담지원 강화 검토</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.600)가 상담수요지수(CDI=0.397)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.203로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 Wee센터 접근성 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.467)가 상담수요지수(CDI=0.272)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.195로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수, Wee센터 접근성 점수, 학교폭력 위험 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>480041720</t>
+          <t>480041216</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>삼랑진고등학교</t>
+          <t>단성고등학교</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -4235,7 +4235,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>밀양시</t>
+          <t>산청군</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -4248,22 +4248,22 @@
         <v>0.4</v>
       </c>
       <c r="H46" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="I46" t="n">
-        <v>0.3357113788902203</v>
+        <v>0.4787365767333901</v>
       </c>
       <c r="J46" t="n">
-        <v>0.1458298191869671</v>
+        <v>0</v>
       </c>
       <c r="K46" t="n">
         <v>0.4666666666666666</v>
       </c>
       <c r="L46" t="n">
-        <v>0.2605137326923958</v>
+        <v>0.27067885891113</v>
       </c>
       <c r="M46" t="n">
-        <v>-0.2061529339742708</v>
+        <v>-0.1959878077555366</v>
       </c>
       <c r="N46" t="inlineStr">
         <is>
@@ -4292,24 +4292,24 @@
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>전문상담교사 배치 또는 순회상담교사 연계 검토; Wee센터 접근성이 낮아 이동형 상담, 온라인 상담, 권역별 연계 강화 검토; 학교폭력 피해 응답률 기반 위험 점수가 높아 학교폭력 관련 상담지원 강화 검토</t>
+          <t>전문상담교사 배치 또는 순회상담교사 연계 검토; Wee센터 접근성이 낮아 이동형 상담, 온라인 상담, 권역별 연계 강화 검토; 실제 상담 이용 수준이 높아 상담 프로그램 확대 또는 상담 인력 보완 검토</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.467)가 상담수요지수(CDI=0.261)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.206로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수, Wee센터 접근성 점수, 학교폭력 위험 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.467)가 상담수요지수(CDI=0.271)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.196로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수, Wee센터 접근성 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>480041253</t>
+          <t>480041496</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>마산용마고등학교</t>
+          <t>웅천고등학교</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -4323,31 +4323,31 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="F47" t="n">
         <v>1</v>
       </c>
       <c r="G47" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="H47" t="n">
         <v>1</v>
       </c>
       <c r="I47" t="n">
-        <v>0.3216038732876896</v>
+        <v>0.1791911099361308</v>
       </c>
       <c r="J47" t="n">
-        <v>0.05768870241755037</v>
+        <v>0.01284796573875803</v>
       </c>
       <c r="K47" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6</v>
       </c>
       <c r="L47" t="n">
-        <v>0.4597641919017466</v>
+        <v>0.3973463585582963</v>
       </c>
       <c r="M47" t="n">
-        <v>-0.20690247476492</v>
+        <v>-0.2026536414417037</v>
       </c>
       <c r="N47" t="inlineStr">
         <is>
@@ -4366,34 +4366,34 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>B. 수요높음-공급높음</t>
+          <t>A. 수요높음-공급낮음</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>고수요 학교 모니터링 및 프로그램 강화</t>
+          <t>수요-공급 불균형 우선 개선</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>전문상담교사 배치 또는 순회상담교사 연계 검토; 대규모 학교로 상담수요 규모가 커 상담 인력 보강 검토</t>
+          <t>Wee센터 접근성이 낮아 이동형 상담, 온라인 상담, 권역별 연계 강화 검토; 대규모 학교로 상담수요 규모가 커 상담 인력 보강 검토</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.460)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.207로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.600)가 상담수요지수(CDI=0.397)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.203로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 Wee센터 접근성 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>480041216</t>
+          <t>480041253</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>단성고등학교</t>
+          <t>마산용마고등학교</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -4403,7 +4403,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>산청군</t>
+          <t>창원시</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -4413,25 +4413,25 @@
         <v>1</v>
       </c>
       <c r="G48" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="H48" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="I48" t="n">
-        <v>0.4787365767333901</v>
+        <v>0.3216038732876896</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>0.05768870241755037</v>
       </c>
       <c r="K48" t="n">
-        <v>0.4666666666666666</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="L48" t="n">
-        <v>0.25957885891113</v>
+        <v>0.4597641919017466</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.2070878077555366</v>
+        <v>-0.20690247476492</v>
       </c>
       <c r="N48" t="inlineStr">
         <is>
@@ -4440,32 +4440,32 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>공급 보통</t>
+          <t>공급 양호</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>수요 낮음</t>
+          <t>수요 보통</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>C. 수요낮음-공급낮음</t>
+          <t>B. 수요높음-공급높음</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>권역별 순회상담 또는 최소 인프라 보완</t>
+          <t>고수요 학교 모니터링 및 프로그램 강화</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>전문상담교사 배치 또는 순회상담교사 연계 검토; Wee센터 접근성이 낮아 이동형 상담, 온라인 상담, 권역별 연계 강화 검토; 실제 상담 이용 수준이 높아 상담 프로그램 확대 또는 상담 인력 보완 검토</t>
+          <t>전문상담교사 배치 또는 순회상담교사 연계 검토; 대규모 학교로 상담수요 규모가 커 상담 인력 보강 검토</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.467)가 상담수요지수(CDI=0.260)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.207로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수, Wee센터 접근성 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.460)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.207로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
@@ -6320,12 +6320,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>480041478</t>
+          <t>480041390</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>창원신월고등학교</t>
+          <t>진교고등학교</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -6335,35 +6335,35 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>창원시</t>
+          <t>하동군</t>
         </is>
       </c>
       <c r="E71" t="n">
+        <v>1</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" t="n">
         <v>0.4</v>
       </c>
-      <c r="F71" t="n">
-        <v>1</v>
-      </c>
-      <c r="G71" t="n">
-        <v>1</v>
-      </c>
       <c r="H71" t="n">
-        <v>1</v>
+        <v>0.3333</v>
       </c>
       <c r="I71" t="n">
-        <v>0.4646971034293428</v>
+        <v>0.265045797380282</v>
       </c>
       <c r="J71" t="n">
-        <v>0.1011385011385011</v>
+        <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>0.7999999999999999</v>
+        <v>0.4666666666666666</v>
       </c>
       <c r="L71" t="n">
-        <v>0.5219452015226146</v>
+        <v>0.1994485991267606</v>
       </c>
       <c r="M71" t="n">
-        <v>-0.2780547984773853</v>
+        <v>-0.267218067539906</v>
       </c>
       <c r="N71" t="inlineStr">
         <is>
@@ -6372,44 +6372,44 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>공급 양호</t>
+          <t>공급 보통</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>수요 보통</t>
+          <t>수요 낮음</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>B. 수요높음-공급높음</t>
+          <t>C. 수요낮음-공급낮음</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>고수요 학교 모니터링 및 프로그램 강화</t>
+          <t>권역별 순회상담 또는 최소 인프라 보완</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>대규모 학교로 상담수요 규모가 커 상담 인력 보강 검토; 실제 상담 이용 수준이 높아 상담 프로그램 확대 또는 상담 인력 보완 검토</t>
+          <t>Wee클래스 신설 또는 운영 현황 재확인 검토; Wee센터 접근성이 낮아 이동형 상담, 온라인 상담, 권역별 연계 강화 검토</t>
         </is>
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.522)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.278로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.467)가 상담수요지수(CDI=0.199)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.267로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 Wee클래스 미운영, Wee센터 접근성 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>480041390</t>
+          <t>480041642</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>진교고등학교</t>
+          <t>군북고등학교</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -6419,35 +6419,35 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>하동군</t>
+          <t>함안군</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G72" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="H72" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="I72" t="n">
-        <v>0.265045797380282</v>
+        <v>0.4940415218194545</v>
       </c>
       <c r="J72" t="n">
-        <v>0</v>
+        <v>0.03973509933774835</v>
       </c>
       <c r="K72" t="n">
-        <v>0.4666666666666666</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="L72" t="n">
-        <v>0.1883485991267607</v>
+        <v>0.2890255403857342</v>
       </c>
       <c r="M72" t="n">
-        <v>-0.278318067539906</v>
+        <v>-0.2776411262809325</v>
       </c>
       <c r="N72" t="inlineStr">
         <is>
@@ -6476,24 +6476,24 @@
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>Wee클래스 신설 또는 운영 현황 재확인 검토; Wee센터 접근성이 낮아 이동형 상담, 온라인 상담, 권역별 연계 강화 검토</t>
+          <t>전문상담교사 배치 또는 순회상담교사 연계 검토; 실제 상담 이용 수준이 높아 상담 프로그램 확대 또는 상담 인력 보완 검토</t>
         </is>
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.467)가 상담수요지수(CDI=0.188)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.278로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 Wee클래스 미운영, Wee센터 접근성 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.567)가 상담수요지수(CDI=0.289)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.278로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>480041642</t>
+          <t>480041478</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>군북고등학교</t>
+          <t>창원신월고등학교</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -6503,35 +6503,35 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>함안군</t>
+          <t>창원시</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="F73" t="n">
         <v>1</v>
       </c>
       <c r="G73" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="H73" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="I73" t="n">
-        <v>0.4940415218194545</v>
+        <v>0.4646971034293428</v>
       </c>
       <c r="J73" t="n">
-        <v>0.03973509933774835</v>
+        <v>0.1011385011385011</v>
       </c>
       <c r="K73" t="n">
-        <v>0.5666666666666667</v>
+        <v>0.7999999999999999</v>
       </c>
       <c r="L73" t="n">
-        <v>0.2779255403857343</v>
+        <v>0.5219452015226146</v>
       </c>
       <c r="M73" t="n">
-        <v>-0.2887411262809323</v>
+        <v>-0.2780547984773853</v>
       </c>
       <c r="N73" t="inlineStr">
         <is>
@@ -6540,44 +6540,44 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>공급 보통</t>
+          <t>공급 양호</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>수요 낮음</t>
+          <t>수요 보통</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>C. 수요낮음-공급낮음</t>
+          <t>B. 수요높음-공급높음</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>권역별 순회상담 또는 최소 인프라 보완</t>
+          <t>고수요 학교 모니터링 및 프로그램 강화</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>전문상담교사 배치 또는 순회상담교사 연계 검토; 실제 상담 이용 수준이 높아 상담 프로그램 확대 또는 상담 인력 보완 검토</t>
+          <t>대규모 학교로 상담수요 규모가 커 상담 인력 보강 검토; 실제 상담 이용 수준이 높아 상담 프로그램 확대 또는 상담 인력 보완 검토</t>
         </is>
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.567)가 상담수요지수(CDI=0.278)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.289로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.522)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.278로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>480041848</t>
+          <t>480041645</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>진해중앙고등학교</t>
+          <t>김해중앙여자고등학교</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -6587,35 +6587,35 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>창원시</t>
+          <t>김해시</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="F74" t="n">
         <v>1</v>
       </c>
       <c r="G74" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="H74" t="n">
-        <v>1</v>
+        <v>0.6667</v>
       </c>
       <c r="I74" t="n">
-        <v>0.1905781927899014</v>
+        <v>0.3871806223139501</v>
       </c>
       <c r="J74" t="n">
-        <v>0.0403078947608462</v>
+        <v>0.1075804776739356</v>
       </c>
       <c r="K74" t="n">
-        <v>0.6999999999999998</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="L74" t="n">
-        <v>0.4102953625169158</v>
+        <v>0.3871536999959619</v>
       </c>
       <c r="M74" t="n">
-        <v>-0.2897046374830841</v>
+        <v>-0.2795129666707047</v>
       </c>
       <c r="N74" t="inlineStr">
         <is>
@@ -6644,24 +6644,24 @@
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>대규모 학교로 상담수요 규모가 커 상담 인력 보강 검토</t>
+          <t>전문상담교사 배치 또는 순회상담교사 연계 검토</t>
         </is>
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.700)가 상담수요지수(CDI=0.410)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.290로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.387)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.280로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>480041510</t>
+          <t>480041547</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>통영고등학교</t>
+          <t>함안고등학교</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -6671,35 +6671,35 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>통영시</t>
+          <t>함안군</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="F75" t="n">
         <v>1</v>
       </c>
       <c r="G75" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="H75" t="n">
-        <v>1</v>
+        <v>0.6667</v>
       </c>
       <c r="I75" t="n">
-        <v>0.1538793933695575</v>
+        <v>0.3375120411071955</v>
       </c>
       <c r="J75" t="n">
-        <v>0.05379758396546978</v>
+        <v>0.1446991957387437</v>
       </c>
       <c r="K75" t="n">
-        <v>0.6999999999999998</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="L75" t="n">
-        <v>0.4025589924450091</v>
+        <v>0.3829704122819798</v>
       </c>
       <c r="M75" t="n">
-        <v>-0.2974410075549908</v>
+        <v>-0.2836962543846868</v>
       </c>
       <c r="N75" t="inlineStr">
         <is>
@@ -6728,24 +6728,24 @@
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>대규모 학교로 상담수요 규모가 커 상담 인력 보강 검토</t>
+          <t>전문상담교사 배치 또는 순회상담교사 연계 검토; 학교폭력 피해 응답률 기반 위험 점수가 높아 학교폭력 관련 상담지원 강화 검토</t>
         </is>
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.700)가 상담수요지수(CDI=0.403)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.297로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.383)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.284로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수, 학교폭력 위험 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>480041870</t>
+          <t>480041848</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>창신고등학교</t>
+          <t>진해중앙고등학교</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -6759,31 +6759,31 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="F76" t="n">
         <v>1</v>
       </c>
       <c r="G76" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="H76" t="n">
         <v>1</v>
       </c>
       <c r="I76" t="n">
-        <v>0.0364645107070795</v>
+        <v>0.1905781927899014</v>
       </c>
       <c r="J76" t="n">
-        <v>0.06971291371247043</v>
+        <v>0.0403078947608462</v>
       </c>
       <c r="K76" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="L76" t="n">
-        <v>0.36872580813985</v>
+        <v>0.4102953625169158</v>
       </c>
       <c r="M76" t="n">
-        <v>-0.2979408585268166</v>
+        <v>-0.2897046374830841</v>
       </c>
       <c r="N76" t="inlineStr">
         <is>
@@ -6802,34 +6802,34 @@
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>D. 수요낮음-공급높음</t>
+          <t>B. 수요높음-공급높음</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>현 수준 유지 또는 거점학교 활용</t>
+          <t>고수요 학교 모니터링 및 프로그램 강화</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>전문상담교사 배치 또는 순회상담교사 연계 검토; 대규모 학교로 상담수요 규모가 커 상담 인력 보강 검토</t>
+          <t>대규모 학교로 상담수요 규모가 커 상담 인력 보강 검토</t>
         </is>
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.369)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.298로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.700)가 상담수요지수(CDI=0.410)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.290로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>480041221</t>
+          <t>480041510</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>창원북면고등학교</t>
+          <t>통영고등학교</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -6839,7 +6839,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>창원시</t>
+          <t>통영시</t>
         </is>
       </c>
       <c r="E77" t="n">
@@ -6855,19 +6855,19 @@
         <v>1</v>
       </c>
       <c r="I77" t="n">
-        <v>0.1144698988881103</v>
+        <v>0.1538793933695575</v>
       </c>
       <c r="J77" t="n">
-        <v>0.08689989448694277</v>
+        <v>0.05379758396546978</v>
       </c>
       <c r="K77" t="n">
         <v>0.6999999999999998</v>
       </c>
       <c r="L77" t="n">
-        <v>0.4004565977916844</v>
+        <v>0.4025589924450091</v>
       </c>
       <c r="M77" t="n">
-        <v>-0.2995434022083154</v>
+        <v>-0.2974410075549908</v>
       </c>
       <c r="N77" t="inlineStr">
         <is>
@@ -6901,19 +6901,19 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.700)가 상담수요지수(CDI=0.400)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.300로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.700)가 상담수요지수(CDI=0.403)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.297로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>480041645</t>
+          <t>480041870</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>김해중앙여자고등학교</t>
+          <t>창신고등학교</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -6923,7 +6923,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>김해시</t>
+          <t>창원시</t>
         </is>
       </c>
       <c r="E78" t="n">
@@ -6936,22 +6936,22 @@
         <v>1</v>
       </c>
       <c r="H78" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="I78" t="n">
-        <v>0.3871806223139501</v>
+        <v>0.0364645107070795</v>
       </c>
       <c r="J78" t="n">
-        <v>0.1075804776739356</v>
+        <v>0.06971291371247043</v>
       </c>
       <c r="K78" t="n">
         <v>0.6666666666666666</v>
       </c>
       <c r="L78" t="n">
-        <v>0.3649203666626286</v>
+        <v>0.36872580813985</v>
       </c>
       <c r="M78" t="n">
-        <v>-0.301746300004038</v>
+        <v>-0.2979408585268166</v>
       </c>
       <c r="N78" t="inlineStr">
         <is>
@@ -6980,24 +6980,24 @@
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>전문상담교사 배치 또는 순회상담교사 연계 검토</t>
+          <t>전문상담교사 배치 또는 순회상담교사 연계 검토; 대규모 학교로 상담수요 규모가 커 상담 인력 보강 검토</t>
         </is>
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.365)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.302로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.369)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.298로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>480041547</t>
+          <t>480041221</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>함안고등학교</t>
+          <t>창원북면고등학교</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -7007,35 +7007,35 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>함안군</t>
+          <t>창원시</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="F79" t="n">
         <v>1</v>
       </c>
       <c r="G79" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="H79" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="I79" t="n">
-        <v>0.3375120411071955</v>
+        <v>0.1144698988881103</v>
       </c>
       <c r="J79" t="n">
-        <v>0.1446991957387437</v>
+        <v>0.08689989448694277</v>
       </c>
       <c r="K79" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="L79" t="n">
-        <v>0.3607370789486464</v>
+        <v>0.4004565977916844</v>
       </c>
       <c r="M79" t="n">
-        <v>-0.3059295877180203</v>
+        <v>-0.2995434022083154</v>
       </c>
       <c r="N79" t="inlineStr">
         <is>
@@ -7054,34 +7054,34 @@
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>D. 수요낮음-공급높음</t>
+          <t>B. 수요높음-공급높음</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>현 수준 유지 또는 거점학교 활용</t>
+          <t>고수요 학교 모니터링 및 프로그램 강화</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>전문상담교사 배치 또는 순회상담교사 연계 검토; 학교폭력 피해 응답률 기반 위험 점수가 높아 학교폭력 관련 상담지원 강화 검토</t>
+          <t>대규모 학교로 상담수요 규모가 커 상담 인력 보강 검토</t>
         </is>
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.361)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.306로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수, 학교폭력 위험 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.700)가 상담수요지수(CDI=0.400)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.300로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>480041440</t>
+          <t>480041255</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>진주고등학교</t>
+          <t>마산구암고등학교</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -7091,11 +7091,11 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>진주시</t>
+          <t>창원시</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="F80" t="n">
         <v>1</v>
@@ -7104,22 +7104,22 @@
         <v>1</v>
       </c>
       <c r="H80" t="n">
-        <v>1</v>
+        <v>0.6667</v>
       </c>
       <c r="I80" t="n">
-        <v>0.4092675560543229</v>
+        <v>0.3527345051160103</v>
       </c>
       <c r="J80" t="n">
-        <v>0.06253203028192925</v>
+        <v>0.07477909683725838</v>
       </c>
       <c r="K80" t="n">
-        <v>0.7999999999999999</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="L80" t="n">
-        <v>0.490599862112084</v>
+        <v>0.3647378673177562</v>
       </c>
       <c r="M80" t="n">
-        <v>-0.3094001378879159</v>
+        <v>-0.3019287993489104</v>
       </c>
       <c r="N80" t="inlineStr">
         <is>
@@ -7138,34 +7138,34 @@
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>B. 수요높음-공급높음</t>
+          <t>D. 수요낮음-공급높음</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>고수요 학교 모니터링 및 프로그램 강화</t>
+          <t>현 수준 유지 또는 거점학교 활용</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>대규모 학교로 상담수요 규모가 커 상담 인력 보강 검토; 실제 상담 이용 수준이 높아 상담 프로그램 확대 또는 상담 인력 보완 검토</t>
+          <t>전문상담교사 배치 또는 순회상담교사 연계 검토</t>
         </is>
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.491)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.309로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.365)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.302로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>480041476</t>
+          <t>480041310</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>창원사파고등학교</t>
+          <t>삼천포중앙고등학교</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -7175,11 +7175,11 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>창원시</t>
+          <t>사천시</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="F81" t="n">
         <v>1</v>
@@ -7188,22 +7188,22 @@
         <v>1</v>
       </c>
       <c r="H81" t="n">
-        <v>1</v>
+        <v>0.6667</v>
       </c>
       <c r="I81" t="n">
-        <v>0.3633825515229166</v>
+        <v>0.3886228313634106</v>
       </c>
       <c r="J81" t="n">
-        <v>0.06537634408602151</v>
+        <v>0.03680981595092025</v>
       </c>
       <c r="K81" t="n">
-        <v>0.7999999999999999</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="L81" t="n">
-        <v>0.4762529652029794</v>
+        <v>0.3640442157714436</v>
       </c>
       <c r="M81" t="n">
-        <v>-0.3237470347970205</v>
+        <v>-0.302622450895223</v>
       </c>
       <c r="N81" t="inlineStr">
         <is>
@@ -7222,34 +7222,34 @@
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>B. 수요높음-공급높음</t>
+          <t>D. 수요낮음-공급높음</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>고수요 학교 모니터링 및 프로그램 강화</t>
+          <t>현 수준 유지 또는 거점학교 활용</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>대규모 학교로 상담수요 규모가 커 상담 인력 보강 검토</t>
+          <t>전문상담교사 배치 또는 순회상담교사 연계 검토; 실제 상담 이용 수준이 높아 상담 프로그램 확대 또는 상담 인력 보완 검토</t>
         </is>
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.476)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.324로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.364)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.303로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>480041255</t>
+          <t>480041878</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>마산구암고등학교</t>
+          <t>창원경일여자고등학교</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -7272,22 +7272,22 @@
         <v>1</v>
       </c>
       <c r="H82" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="I82" t="n">
-        <v>0.3527345051160103</v>
+        <v>0.3410131426255853</v>
       </c>
       <c r="J82" t="n">
-        <v>0.07477909683725838</v>
+        <v>0.0823202833349287</v>
       </c>
       <c r="K82" t="n">
         <v>0.6666666666666666</v>
       </c>
       <c r="L82" t="n">
-        <v>0.3425045339844229</v>
+        <v>0.3633444753201713</v>
       </c>
       <c r="M82" t="n">
-        <v>-0.3241621326822438</v>
+        <v>-0.3033221913464954</v>
       </c>
       <c r="N82" t="inlineStr">
         <is>
@@ -7321,19 +7321,19 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.343)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.324로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.363)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.303로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>480041310</t>
+          <t>480041377</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>삼천포중앙고등학교</t>
+          <t>김해임호고등학교</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -7343,7 +7343,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>사천시</t>
+          <t>김해시</t>
         </is>
       </c>
       <c r="E83" t="n">
@@ -7356,22 +7356,22 @@
         <v>1</v>
       </c>
       <c r="H83" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="I83" t="n">
-        <v>0.3886228313634106</v>
+        <v>0.3042280023489025</v>
       </c>
       <c r="J83" t="n">
-        <v>0.03680981595092025</v>
+        <v>0.1033769063180828</v>
       </c>
       <c r="K83" t="n">
         <v>0.6666666666666666</v>
       </c>
       <c r="L83" t="n">
-        <v>0.3418108824381103</v>
+        <v>0.3581016362223284</v>
       </c>
       <c r="M83" t="n">
-        <v>-0.3248557842285563</v>
+        <v>-0.3085650304443383</v>
       </c>
       <c r="N83" t="inlineStr">
         <is>
@@ -7400,24 +7400,24 @@
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>전문상담교사 배치 또는 순회상담교사 연계 검토; 실제 상담 이용 수준이 높아 상담 프로그램 확대 또는 상담 인력 보완 검토</t>
+          <t>전문상담교사 배치 또는 순회상담교사 연계 검토</t>
         </is>
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.342)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.325로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.358)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.309로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>480041878</t>
+          <t>480041440</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>창원경일여자고등학교</t>
+          <t>진주고등학교</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -7427,11 +7427,11 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>창원시</t>
+          <t>진주시</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="F84" t="n">
         <v>1</v>
@@ -7440,22 +7440,22 @@
         <v>1</v>
       </c>
       <c r="H84" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="I84" t="n">
-        <v>0.3410131426255853</v>
+        <v>0.4092675560543229</v>
       </c>
       <c r="J84" t="n">
-        <v>0.0823202833349287</v>
+        <v>0.06253203028192925</v>
       </c>
       <c r="K84" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7999999999999999</v>
       </c>
       <c r="L84" t="n">
-        <v>0.341111141986838</v>
+        <v>0.490599862112084</v>
       </c>
       <c r="M84" t="n">
-        <v>-0.3255555246798286</v>
+        <v>-0.3094001378879159</v>
       </c>
       <c r="N84" t="inlineStr">
         <is>
@@ -7474,34 +7474,34 @@
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>D. 수요낮음-공급높음</t>
+          <t>B. 수요높음-공급높음</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>현 수준 유지 또는 거점학교 활용</t>
+          <t>고수요 학교 모니터링 및 프로그램 강화</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>전문상담교사 배치 또는 순회상담교사 연계 검토</t>
+          <t>대규모 학교로 상담수요 규모가 커 상담 인력 보강 검토; 실제 상담 이용 수준이 높아 상담 프로그램 확대 또는 상담 인력 보완 검토</t>
         </is>
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.341)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.326로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.491)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.309로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>480041177</t>
+          <t>480041215</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>김해경원고등학교</t>
+          <t>남해제일고등학교</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -7511,11 +7511,11 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>김해시</t>
+          <t>남해군</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="F85" t="n">
         <v>1</v>
@@ -7524,22 +7524,22 @@
         <v>1</v>
       </c>
       <c r="H85" t="n">
-        <v>1</v>
+        <v>0.6667</v>
       </c>
       <c r="I85" t="n">
-        <v>0.325164981619064</v>
+        <v>0.2624588353774778</v>
       </c>
       <c r="J85" t="n">
-        <v>0.0933794595346976</v>
+        <v>0.1367267283323531</v>
       </c>
       <c r="K85" t="n">
-        <v>0.7999999999999999</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="L85" t="n">
-        <v>0.4728481470512538</v>
+        <v>0.355295187903277</v>
       </c>
       <c r="M85" t="n">
-        <v>-0.3271518529487462</v>
+        <v>-0.3113714787633896</v>
       </c>
       <c r="N85" t="inlineStr">
         <is>
@@ -7558,34 +7558,34 @@
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>B. 수요높음-공급높음</t>
+          <t>D. 수요낮음-공급높음</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>고수요 학교 모니터링 및 프로그램 강화</t>
+          <t>현 수준 유지 또는 거점학교 활용</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>대규모 학교로 상담수요 규모가 커 상담 인력 보강 검토</t>
+          <t>전문상담교사 배치 또는 순회상담교사 연계 검토; 학교폭력 피해 응답률 기반 위험 점수가 높아 학교폭력 관련 상담지원 강화 검토</t>
         </is>
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.473)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.327로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.355)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.311로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수, 학교폭력 위험 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>480041377</t>
+          <t>480041476</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>김해임호고등학교</t>
+          <t>창원사파고등학교</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -7595,11 +7595,11 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>김해시</t>
+          <t>창원시</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="F86" t="n">
         <v>1</v>
@@ -7608,22 +7608,22 @@
         <v>1</v>
       </c>
       <c r="H86" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="I86" t="n">
-        <v>0.3042280023489025</v>
+        <v>0.3633825515229166</v>
       </c>
       <c r="J86" t="n">
-        <v>0.1033769063180828</v>
+        <v>0.06537634408602151</v>
       </c>
       <c r="K86" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7999999999999999</v>
       </c>
       <c r="L86" t="n">
-        <v>0.3358683028889951</v>
+        <v>0.4762529652029794</v>
       </c>
       <c r="M86" t="n">
-        <v>-0.3307983637776715</v>
+        <v>-0.3237470347970205</v>
       </c>
       <c r="N86" t="inlineStr">
         <is>
@@ -7642,34 +7642,34 @@
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>D. 수요낮음-공급높음</t>
+          <t>B. 수요높음-공급높음</t>
         </is>
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>현 수준 유지 또는 거점학교 활용</t>
+          <t>고수요 학교 모니터링 및 프로그램 강화</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>전문상담교사 배치 또는 순회상담교사 연계 검토</t>
+          <t>대규모 학교로 상담수요 규모가 커 상담 인력 보강 검토</t>
         </is>
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.336)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.331로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.476)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.324로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>480041946</t>
+          <t>480041177</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>거제상문고등학교</t>
+          <t>김해경원고등학교</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>거제시</t>
+          <t>김해시</t>
         </is>
       </c>
       <c r="E87" t="n">
@@ -7695,19 +7695,19 @@
         <v>1</v>
       </c>
       <c r="I87" t="n">
-        <v>0.3326468748350401</v>
+        <v>0.325164981619064</v>
       </c>
       <c r="J87" t="n">
-        <v>0.07464120483687738</v>
+        <v>0.0933794595346976</v>
       </c>
       <c r="K87" t="n">
         <v>0.7999999999999999</v>
       </c>
       <c r="L87" t="n">
-        <v>0.4690960265573058</v>
+        <v>0.4728481470512538</v>
       </c>
       <c r="M87" t="n">
-        <v>-0.3309039734426941</v>
+        <v>-0.3271518529487462</v>
       </c>
       <c r="N87" t="inlineStr">
         <is>
@@ -7741,19 +7741,19 @@
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.469)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.331로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.473)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.327로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>480041704</t>
+          <t>480041946</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>마산무학여자고등학교</t>
+          <t>거제상문고등학교</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>창원시</t>
+          <t>거제시</t>
         </is>
       </c>
       <c r="E88" t="n">
@@ -7779,19 +7779,19 @@
         <v>1</v>
       </c>
       <c r="I88" t="n">
-        <v>0.3585012688069095</v>
+        <v>0.3326468748350401</v>
       </c>
       <c r="J88" t="n">
-        <v>0.04616358873301335</v>
+        <v>0.07464120483687738</v>
       </c>
       <c r="K88" t="n">
         <v>0.7999999999999999</v>
       </c>
       <c r="L88" t="n">
-        <v>0.4682216191799743</v>
+        <v>0.4690960265573058</v>
       </c>
       <c r="M88" t="n">
-        <v>-0.3317783808200256</v>
+        <v>-0.3309039734426941</v>
       </c>
       <c r="N88" t="inlineStr">
         <is>
@@ -7825,19 +7825,19 @@
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.468)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.332로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.469)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.331로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>480041215</t>
+          <t>480041704</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>남해제일고등학교</t>
+          <t>마산무학여자고등학교</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -7847,11 +7847,11 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>남해군</t>
+          <t>창원시</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="F89" t="n">
         <v>1</v>
@@ -7860,22 +7860,22 @@
         <v>1</v>
       </c>
       <c r="H89" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="I89" t="n">
-        <v>0.2624588353774778</v>
+        <v>0.3585012688069095</v>
       </c>
       <c r="J89" t="n">
-        <v>0.1367267283323531</v>
+        <v>0.04616358873301335</v>
       </c>
       <c r="K89" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7999999999999999</v>
       </c>
       <c r="L89" t="n">
-        <v>0.3330618545699436</v>
+        <v>0.4682216191799743</v>
       </c>
       <c r="M89" t="n">
-        <v>-0.333604812096723</v>
+        <v>-0.3317783808200256</v>
       </c>
       <c r="N89" t="inlineStr">
         <is>
@@ -7894,34 +7894,34 @@
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>D. 수요낮음-공급높음</t>
+          <t>B. 수요높음-공급높음</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>현 수준 유지 또는 거점학교 활용</t>
+          <t>고수요 학교 모니터링 및 프로그램 강화</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>전문상담교사 배치 또는 순회상담교사 연계 검토; 학교폭력 피해 응답률 기반 위험 점수가 높아 학교폭력 관련 상담지원 강화 검토</t>
+          <t>대규모 학교로 상담수요 규모가 커 상담 인력 보강 검토</t>
         </is>
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.333)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.334로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수, 학교폭력 위험 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.468)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.332로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>480041560</t>
+          <t>480041876</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>합포고등학교</t>
+          <t>창원경일고등학교</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -7935,7 +7935,7 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="F90" t="n">
         <v>1</v>
@@ -7944,22 +7944,22 @@
         <v>1</v>
       </c>
       <c r="H90" t="n">
-        <v>1</v>
+        <v>0.6667</v>
       </c>
       <c r="I90" t="n">
-        <v>0.3186340225512735</v>
+        <v>0.295967901342231</v>
       </c>
       <c r="J90" t="n">
-        <v>0.07371730382293762</v>
+        <v>0.0411237298266587</v>
       </c>
       <c r="K90" t="n">
-        <v>0.7999999999999999</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="L90" t="n">
-        <v>0.4641171087914038</v>
+        <v>0.3345972103896299</v>
       </c>
       <c r="M90" t="n">
-        <v>-0.3358828912085962</v>
+        <v>-0.3320694562770367</v>
       </c>
       <c r="N90" t="inlineStr">
         <is>
@@ -7978,34 +7978,34 @@
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>B. 수요높음-공급높음</t>
+          <t>D. 수요낮음-공급높음</t>
         </is>
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>고수요 학교 모니터링 및 프로그램 강화</t>
+          <t>현 수준 유지 또는 거점학교 활용</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>대규모 학교로 상담수요 규모가 커 상담 인력 보강 검토</t>
+          <t>전문상담교사 배치 또는 순회상담교사 연계 검토</t>
         </is>
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.464)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.336로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.335)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.332로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>480041936</t>
+          <t>480041768</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>물금고등학교</t>
+          <t>세종고등학교</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -8015,11 +8015,11 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>양산시</t>
+          <t>밀양시</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="F91" t="n">
         <v>1</v>
@@ -8028,22 +8028,22 @@
         <v>1</v>
       </c>
       <c r="H91" t="n">
-        <v>1</v>
+        <v>0.6667</v>
       </c>
       <c r="I91" t="n">
-        <v>0.2848459134604937</v>
+        <v>0.2655110230628451</v>
       </c>
       <c r="J91" t="n">
-        <v>0.1047625000482329</v>
+        <v>0.0682096711781313</v>
       </c>
       <c r="K91" t="n">
-        <v>0.7999999999999999</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="L91" t="n">
-        <v>0.4632028045029088</v>
+        <v>0.3334735647469921</v>
       </c>
       <c r="M91" t="n">
-        <v>-0.3367971954970911</v>
+        <v>-0.3331931019196746</v>
       </c>
       <c r="N91" t="inlineStr">
         <is>
@@ -8062,34 +8062,34 @@
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>B. 수요높음-공급높음</t>
+          <t>D. 수요낮음-공급높음</t>
         </is>
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>고수요 학교 모니터링 및 프로그램 강화</t>
+          <t>현 수준 유지 또는 거점학교 활용</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>대규모 학교로 상담수요 규모가 커 상담 인력 보강 검토</t>
+          <t>전문상담교사 배치 또는 순회상담교사 연계 검토</t>
         </is>
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.463)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.337로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.333)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.333로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>480041325</t>
+          <t>480041550</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>진주중앙고등학교</t>
+          <t>함양고등학교</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -8099,11 +8099,11 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>진주시</t>
+          <t>함양군</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="F92" t="n">
         <v>1</v>
@@ -8112,22 +8112,22 @@
         <v>1</v>
       </c>
       <c r="H92" t="n">
-        <v>1</v>
+        <v>0.6667</v>
       </c>
       <c r="I92" t="n">
-        <v>0.3059509962586563</v>
+        <v>0.215535457316114</v>
       </c>
       <c r="J92" t="n">
-        <v>0.08280695283323346</v>
+        <v>0.1129521918002553</v>
       </c>
       <c r="K92" t="n">
-        <v>0.7999999999999999</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="L92" t="n">
-        <v>0.4629193163639632</v>
+        <v>0.3317292163721231</v>
       </c>
       <c r="M92" t="n">
-        <v>-0.3370806836360367</v>
+        <v>-0.3349374502945435</v>
       </c>
       <c r="N92" t="inlineStr">
         <is>
@@ -8146,34 +8146,34 @@
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>B. 수요높음-공급높음</t>
+          <t>D. 수요낮음-공급높음</t>
         </is>
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>고수요 학교 모니터링 및 프로그램 강화</t>
+          <t>현 수준 유지 또는 거점학교 활용</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>대규모 학교로 상담수요 규모가 커 상담 인력 보강 검토</t>
+          <t>전문상담교사 배치 또는 순회상담교사 연계 검토</t>
         </is>
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.463)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.337로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.332)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.335로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>480041490</t>
+          <t>480041560</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>창원중앙고등학교</t>
+          <t>합포고등학교</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -8199,19 +8199,19 @@
         <v>1</v>
       </c>
       <c r="I93" t="n">
-        <v>0.3076451994709415</v>
+        <v>0.3186340225512735</v>
       </c>
       <c r="J93" t="n">
-        <v>0.08042049605698119</v>
+        <v>0.07371730382293762</v>
       </c>
       <c r="K93" t="n">
         <v>0.7999999999999999</v>
       </c>
       <c r="L93" t="n">
-        <v>0.4626885651759742</v>
+        <v>0.4641171087914038</v>
       </c>
       <c r="M93" t="n">
-        <v>-0.3373114348240258</v>
+        <v>-0.3358828912085962</v>
       </c>
       <c r="N93" t="inlineStr">
         <is>
@@ -8245,19 +8245,19 @@
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.463)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.337로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.464)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.336로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>480041450</t>
+          <t>480041936</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>진주여자고등학교</t>
+          <t>물금고등학교</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -8267,7 +8267,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>진주시</t>
+          <t>양산시</t>
         </is>
       </c>
       <c r="E94" t="n">
@@ -8283,19 +8283,19 @@
         <v>1</v>
       </c>
       <c r="I94" t="n">
-        <v>0.291193675268403</v>
+        <v>0.2848459134604937</v>
       </c>
       <c r="J94" t="n">
-        <v>0.09369861612509398</v>
+        <v>0.1047625000482329</v>
       </c>
       <c r="K94" t="n">
         <v>0.7999999999999999</v>
       </c>
       <c r="L94" t="n">
-        <v>0.4616307637978323</v>
+        <v>0.4632028045029088</v>
       </c>
       <c r="M94" t="n">
-        <v>-0.3383692362021676</v>
+        <v>-0.3367971954970911</v>
       </c>
       <c r="N94" t="inlineStr">
         <is>
@@ -8329,19 +8329,19 @@
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.462)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.338로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.463)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.337로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>480041346</t>
+          <t>480041710</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>김해삼방고등학교</t>
+          <t>영산고등학교</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -8351,35 +8351,35 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>김해시</t>
+          <t>창녕군</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="F95" t="n">
         <v>1</v>
       </c>
       <c r="G95" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="H95" t="n">
-        <v>1</v>
+        <v>0.3333</v>
       </c>
       <c r="I95" t="n">
-        <v>0.2695858144944696</v>
+        <v>0.2296776803799888</v>
       </c>
       <c r="J95" t="n">
-        <v>0.1065812345637828</v>
+        <v>0.1263094278807413</v>
       </c>
       <c r="K95" t="n">
-        <v>0.7999999999999999</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="L95" t="n">
-        <v>0.4587223496860842</v>
+        <v>0.2297623694202434</v>
       </c>
       <c r="M95" t="n">
-        <v>-0.3412776503139157</v>
+        <v>-0.3369042972464232</v>
       </c>
       <c r="N95" t="inlineStr">
         <is>
@@ -8388,44 +8388,44 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>공급 양호</t>
+          <t>공급 보통</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>수요 보통</t>
+          <t>수요 낮음</t>
         </is>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>B. 수요높음-공급높음</t>
+          <t>C. 수요낮음-공급낮음</t>
         </is>
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>고수요 학교 모니터링 및 프로그램 강화</t>
+          <t>권역별 순회상담 또는 최소 인프라 보완</t>
         </is>
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t>대규모 학교로 상담수요 규모가 커 상담 인력 보강 검토</t>
+          <t>전문상담교사 배치 또는 순회상담교사 연계 검토; 학교폭력 피해 응답률 기반 위험 점수가 높아 학교폭력 관련 상담지원 강화 검토</t>
         </is>
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.459)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.341로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.567)가 상담수요지수(CDI=0.230)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.337로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수, 학교폭력 위험 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>480041710</t>
+          <t>480041325</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>영산고등학교</t>
+          <t>진주중앙고등학교</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -8435,35 +8435,35 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>창녕군</t>
+          <t>진주시</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="F96" t="n">
         <v>1</v>
       </c>
       <c r="G96" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="H96" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="I96" t="n">
-        <v>0.2296776803799888</v>
+        <v>0.3059509962586563</v>
       </c>
       <c r="J96" t="n">
-        <v>0.1263094278807413</v>
+        <v>0.08280695283323346</v>
       </c>
       <c r="K96" t="n">
-        <v>0.5666666666666667</v>
+        <v>0.7999999999999999</v>
       </c>
       <c r="L96" t="n">
-        <v>0.2186623694202433</v>
+        <v>0.4629193163639632</v>
       </c>
       <c r="M96" t="n">
-        <v>-0.3480042972464233</v>
+        <v>-0.3370806836360367</v>
       </c>
       <c r="N96" t="inlineStr">
         <is>
@@ -8472,44 +8472,44 @@
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>공급 보통</t>
+          <t>공급 양호</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>수요 낮음</t>
+          <t>수요 보통</t>
         </is>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>C. 수요낮음-공급낮음</t>
+          <t>B. 수요높음-공급높음</t>
         </is>
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>권역별 순회상담 또는 최소 인프라 보완</t>
+          <t>고수요 학교 모니터링 및 프로그램 강화</t>
         </is>
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>전문상담교사 배치 또는 순회상담교사 연계 검토; 학교폭력 피해 응답률 기반 위험 점수가 높아 학교폭력 관련 상담지원 강화 검토</t>
+          <t>대규모 학교로 상담수요 규모가 커 상담 인력 보강 검토</t>
         </is>
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.567)가 상담수요지수(CDI=0.219)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.348로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수, 학교폭력 위험 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.463)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.337로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>480041876</t>
+          <t>480041490</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>창원경일고등학교</t>
+          <t>창원중앙고등학교</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -8523,7 +8523,7 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="F97" t="n">
         <v>1</v>
@@ -8532,22 +8532,22 @@
         <v>1</v>
       </c>
       <c r="H97" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="I97" t="n">
-        <v>0.295967901342231</v>
+        <v>0.3076451994709415</v>
       </c>
       <c r="J97" t="n">
-        <v>0.0411237298266587</v>
+        <v>0.08042049605698119</v>
       </c>
       <c r="K97" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7999999999999999</v>
       </c>
       <c r="L97" t="n">
-        <v>0.3123638770562966</v>
+        <v>0.4626885651759742</v>
       </c>
       <c r="M97" t="n">
-        <v>-0.35430278961037</v>
+        <v>-0.3373114348240258</v>
       </c>
       <c r="N97" t="inlineStr">
         <is>
@@ -8566,34 +8566,34 @@
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>D. 수요낮음-공급높음</t>
+          <t>B. 수요높음-공급높음</t>
         </is>
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>현 수준 유지 또는 거점학교 활용</t>
+          <t>고수요 학교 모니터링 및 프로그램 강화</t>
         </is>
       </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t>전문상담교사 배치 또는 순회상담교사 연계 검토</t>
+          <t>대규모 학교로 상담수요 규모가 커 상담 인력 보강 검토</t>
         </is>
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.312)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.354로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.463)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.337로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>480041768</t>
+          <t>480041290</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>세종고등학교</t>
+          <t>밀양여자고등학교</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -8616,22 +8616,22 @@
         <v>1</v>
       </c>
       <c r="H98" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="I98" t="n">
-        <v>0.2655110230628451</v>
+        <v>0.3182541452104335</v>
       </c>
       <c r="J98" t="n">
-        <v>0.0682096711781313</v>
+        <v>0</v>
       </c>
       <c r="K98" t="n">
         <v>0.6666666666666666</v>
       </c>
       <c r="L98" t="n">
-        <v>0.3112402314136588</v>
+        <v>0.3283180484034778</v>
       </c>
       <c r="M98" t="n">
-        <v>-0.3554264352530078</v>
+        <v>-0.3383486182631888</v>
       </c>
       <c r="N98" t="inlineStr">
         <is>
@@ -8665,19 +8665,19 @@
       </c>
       <c r="T98" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.311)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.355로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.328)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.338로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>480041550</t>
+          <t>480041450</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>함양고등학교</t>
+          <t>진주여자고등학교</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -8687,11 +8687,11 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>함양군</t>
+          <t>진주시</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="F99" t="n">
         <v>1</v>
@@ -8700,22 +8700,22 @@
         <v>1</v>
       </c>
       <c r="H99" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="I99" t="n">
-        <v>0.215535457316114</v>
+        <v>0.291193675268403</v>
       </c>
       <c r="J99" t="n">
-        <v>0.1129521918002553</v>
+        <v>0.09369861612509398</v>
       </c>
       <c r="K99" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7999999999999999</v>
       </c>
       <c r="L99" t="n">
-        <v>0.3094958830387898</v>
+        <v>0.4616307637978323</v>
       </c>
       <c r="M99" t="n">
-        <v>-0.3571707836278769</v>
+        <v>-0.3383692362021676</v>
       </c>
       <c r="N99" t="inlineStr">
         <is>
@@ -8734,34 +8734,34 @@
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>D. 수요낮음-공급높음</t>
+          <t>B. 수요높음-공급높음</t>
         </is>
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>현 수준 유지 또는 거점학교 활용</t>
+          <t>고수요 학교 모니터링 및 프로그램 강화</t>
         </is>
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t>전문상담교사 배치 또는 순회상담교사 연계 검토</t>
+          <t>대규모 학교로 상담수요 규모가 커 상담 인력 보강 검토</t>
         </is>
       </c>
       <c r="T99" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.309)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.357로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.462)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.338로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>480041290</t>
+          <t>480041050</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>밀양여자고등학교</t>
+          <t>경상국립대학교사범대학부설고등학교</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -8771,7 +8771,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>밀양시</t>
+          <t>진주시</t>
         </is>
       </c>
       <c r="E100" t="n">
@@ -8784,22 +8784,22 @@
         <v>1</v>
       </c>
       <c r="H100" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="I100" t="n">
-        <v>0.3182541452104335</v>
+        <v>0.1958431664988423</v>
       </c>
       <c r="J100" t="n">
-        <v>0</v>
+        <v>0.1203453940470656</v>
       </c>
       <c r="K100" t="n">
         <v>0.6666666666666666</v>
       </c>
       <c r="L100" t="n">
-        <v>0.3060847150701445</v>
+        <v>0.3276295201819693</v>
       </c>
       <c r="M100" t="n">
-        <v>-0.3605819515965221</v>
+        <v>-0.3390371464846973</v>
       </c>
       <c r="N100" t="inlineStr">
         <is>
@@ -8828,24 +8828,24 @@
       </c>
       <c r="S100" t="inlineStr">
         <is>
-          <t>전문상담교사 배치 또는 순회상담교사 연계 검토</t>
+          <t>전문상담교사 배치 또는 순회상담교사 연계 검토; 학교폭력 피해 응답률 기반 위험 점수가 높아 학교폭력 관련 상담지원 강화 검토</t>
         </is>
       </c>
       <c r="T100" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.306)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.361로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.328)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.339로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수, 학교폭력 위험 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>480041050</t>
+          <t>480041346</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>경상국립대학교사범대학부설고등학교</t>
+          <t>김해삼방고등학교</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -8855,11 +8855,11 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>진주시</t>
+          <t>김해시</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="F101" t="n">
         <v>1</v>
@@ -8868,22 +8868,22 @@
         <v>1</v>
       </c>
       <c r="H101" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="I101" t="n">
-        <v>0.1958431664988423</v>
+        <v>0.2695858144944696</v>
       </c>
       <c r="J101" t="n">
-        <v>0.1203453940470656</v>
+        <v>0.1065812345637828</v>
       </c>
       <c r="K101" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7999999999999999</v>
       </c>
       <c r="L101" t="n">
-        <v>0.305396186848636</v>
+        <v>0.4587223496860842</v>
       </c>
       <c r="M101" t="n">
-        <v>-0.3612704798180306</v>
+        <v>-0.3412776503139157</v>
       </c>
       <c r="N101" t="inlineStr">
         <is>
@@ -8902,22 +8902,22 @@
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>D. 수요낮음-공급높음</t>
+          <t>B. 수요높음-공급높음</t>
         </is>
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>현 수준 유지 또는 거점학교 활용</t>
+          <t>고수요 학교 모니터링 및 프로그램 강화</t>
         </is>
       </c>
       <c r="S101" t="inlineStr">
         <is>
-          <t>전문상담교사 배치 또는 순회상담교사 연계 검토; 학교폭력 피해 응답률 기반 위험 점수가 높아 학교폭력 관련 상담지원 강화 검토</t>
+          <t>대규모 학교로 상담수요 규모가 커 상담 인력 보강 검토</t>
         </is>
       </c>
       <c r="T101" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.305)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.361로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수, 학교폭력 위험 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.459)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.341로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
@@ -8952,7 +8952,7 @@
         <v>1</v>
       </c>
       <c r="H102" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="I102" t="n">
         <v>0.261803616952978</v>
@@ -8964,10 +8964,10 @@
         <v>0.6666666666666666</v>
       </c>
       <c r="L102" t="n">
-        <v>0.3021932454519877</v>
+        <v>0.324426578785321</v>
       </c>
       <c r="M102" t="n">
-        <v>-0.3644734212146789</v>
+        <v>-0.3422400878813456</v>
       </c>
       <c r="N102" t="inlineStr">
         <is>
@@ -9001,7 +9001,7 @@
       </c>
       <c r="T102" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.302)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.364로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.324)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.342로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
@@ -9036,7 +9036,7 @@
         <v>1</v>
       </c>
       <c r="H103" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="I103" t="n">
         <v>0.1720348935371041</v>
@@ -9048,10 +9048,10 @@
         <v>0.6666666666666666</v>
       </c>
       <c r="L103" t="n">
-        <v>0.3016455595637816</v>
+        <v>0.323878892897115</v>
       </c>
       <c r="M103" t="n">
-        <v>-0.365021107102885</v>
+        <v>-0.3427877737695516</v>
       </c>
       <c r="N103" t="inlineStr">
         <is>
@@ -9085,19 +9085,19 @@
       </c>
       <c r="T103" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.302)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.365로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수, 학교폭력 위험 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.324)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.343로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수, 학교폭력 위험 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>480041672</t>
+          <t>480041654</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>대아고등학교</t>
+          <t>남해고등학교</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -9107,35 +9107,35 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>진주시</t>
+          <t>남해군</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="F104" t="n">
         <v>1</v>
       </c>
       <c r="G104" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="H104" t="n">
-        <v>1</v>
+        <v>0.6667</v>
       </c>
       <c r="I104" t="n">
-        <v>0.2505327659675062</v>
+        <v>0.5272427649597402</v>
       </c>
       <c r="J104" t="n">
-        <v>0.05434060873858773</v>
+        <v>0.1303571428571429</v>
       </c>
       <c r="K104" t="n">
         <v>0.7999999999999999</v>
       </c>
       <c r="L104" t="n">
-        <v>0.434957791568698</v>
+        <v>0.4414333026056277</v>
       </c>
       <c r="M104" t="n">
-        <v>-0.3650422084313019</v>
+        <v>-0.3585666973943722</v>
       </c>
       <c r="N104" t="inlineStr">
         <is>
@@ -9164,24 +9164,24 @@
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>대규모 학교로 상담수요 규모가 커 상담 인력 보강 검토</t>
+          <t>실제 상담 이용 수준이 높아 상담 프로그램 확대 또는 상담 인력 보완 검토; 학교폭력 피해 응답률 기반 위험 점수가 높아 학교폭력 관련 상담지원 강화 검토</t>
         </is>
       </c>
       <c r="T104" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.435)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.365로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.441)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.359로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 학교폭력 위험 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>480041445</t>
+          <t>480041690</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>증산고등학교</t>
+          <t>마산중앙고등학교</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -9191,11 +9191,11 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>양산시</t>
+          <t>창원시</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="F105" t="n">
         <v>1</v>
@@ -9204,22 +9204,22 @@
         <v>1</v>
       </c>
       <c r="H105" t="n">
-        <v>1</v>
+        <v>0.6667</v>
       </c>
       <c r="I105" t="n">
-        <v>0.2505681075971989</v>
+        <v>0.1751204810202206</v>
       </c>
       <c r="J105" t="n">
-        <v>0.05267763566246426</v>
+        <v>0.07802711107010211</v>
       </c>
       <c r="K105" t="n">
-        <v>0.7999999999999999</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="L105" t="n">
-        <v>0.434415247753221</v>
+        <v>0.3066158640301075</v>
       </c>
       <c r="M105" t="n">
-        <v>-0.3655847522467789</v>
+        <v>-0.3600508026365591</v>
       </c>
       <c r="N105" t="inlineStr">
         <is>
@@ -9238,34 +9238,34 @@
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>B. 수요높음-공급높음</t>
+          <t>D. 수요낮음-공급높음</t>
         </is>
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>고수요 학교 모니터링 및 프로그램 강화</t>
+          <t>현 수준 유지 또는 거점학교 활용</t>
         </is>
       </c>
       <c r="S105" t="inlineStr">
         <is>
-          <t>대규모 학교로 상담수요 규모가 커 상담 인력 보강 검토</t>
+          <t>전문상담교사 배치 또는 순회상담교사 연계 검토</t>
         </is>
       </c>
       <c r="T105" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.434)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.366로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.307)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.360로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>480041786</t>
+          <t>480041672</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>양산제일고등학교</t>
+          <t>대아고등학교</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -9275,7 +9275,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>양산시</t>
+          <t>진주시</t>
         </is>
       </c>
       <c r="E106" t="n">
@@ -9291,19 +9291,19 @@
         <v>1</v>
       </c>
       <c r="I106" t="n">
-        <v>0.2208455207621119</v>
+        <v>0.2505327659675062</v>
       </c>
       <c r="J106" t="n">
-        <v>0.08057910780812105</v>
+        <v>0.05434060873858773</v>
       </c>
       <c r="K106" t="n">
         <v>0.7999999999999999</v>
       </c>
       <c r="L106" t="n">
-        <v>0.433808209523411</v>
+        <v>0.434957791568698</v>
       </c>
       <c r="M106" t="n">
-        <v>-0.366191790476589</v>
+        <v>-0.3650422084313019</v>
       </c>
       <c r="N106" t="inlineStr">
         <is>
@@ -9337,19 +9337,19 @@
       </c>
       <c r="T106" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.434)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.366로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.435)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.365로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>480041355</t>
+          <t>480041445</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>양산남부고등학교</t>
+          <t>증산고등학교</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -9375,19 +9375,19 @@
         <v>1</v>
       </c>
       <c r="I107" t="n">
-        <v>0.191743779384035</v>
+        <v>0.2505681075971989</v>
       </c>
       <c r="J107" t="n">
-        <v>0.102956626419177</v>
+        <v>0.05267763566246426</v>
       </c>
       <c r="K107" t="n">
         <v>0.7999999999999999</v>
       </c>
       <c r="L107" t="n">
-        <v>0.4315668019344041</v>
+        <v>0.434415247753221</v>
       </c>
       <c r="M107" t="n">
-        <v>-0.3684331980655958</v>
+        <v>-0.3655847522467789</v>
       </c>
       <c r="N107" t="inlineStr">
         <is>
@@ -9421,19 +9421,19 @@
       </c>
       <c r="T107" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.432)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.368로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.434)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.366로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>480041931</t>
+          <t>480041786</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>창원대암고등학교</t>
+          <t>양산제일고등학교</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -9443,7 +9443,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>창원시</t>
+          <t>양산시</t>
         </is>
       </c>
       <c r="E108" t="n">
@@ -9459,19 +9459,19 @@
         <v>1</v>
       </c>
       <c r="I108" t="n">
-        <v>0.2152890107824633</v>
+        <v>0.2208455207621119</v>
       </c>
       <c r="J108" t="n">
-        <v>0.05105071094104519</v>
+        <v>0.08057910780812105</v>
       </c>
       <c r="K108" t="n">
         <v>0.7999999999999999</v>
       </c>
       <c r="L108" t="n">
-        <v>0.4221132405745028</v>
+        <v>0.433808209523411</v>
       </c>
       <c r="M108" t="n">
-        <v>-0.3778867594254972</v>
+        <v>-0.366191790476589</v>
       </c>
       <c r="N108" t="inlineStr">
         <is>
@@ -9505,19 +9505,19 @@
       </c>
       <c r="T108" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.422)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.378로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.434)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.366로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>480041654</t>
+          <t>480041355</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>남해고등학교</t>
+          <t>양산남부고등학교</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -9527,35 +9527,35 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>남해군</t>
+          <t>양산시</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="F109" t="n">
         <v>1</v>
       </c>
       <c r="G109" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="H109" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="I109" t="n">
-        <v>0.5272427649597402</v>
+        <v>0.191743779384035</v>
       </c>
       <c r="J109" t="n">
-        <v>0.1303571428571429</v>
+        <v>0.102956626419177</v>
       </c>
       <c r="K109" t="n">
         <v>0.7999999999999999</v>
       </c>
       <c r="L109" t="n">
-        <v>0.4191999692722944</v>
+        <v>0.4315668019344041</v>
       </c>
       <c r="M109" t="n">
-        <v>-0.3808000307277055</v>
+        <v>-0.3684331980655958</v>
       </c>
       <c r="N109" t="inlineStr">
         <is>
@@ -9584,24 +9584,24 @@
       </c>
       <c r="S109" t="inlineStr">
         <is>
-          <t>실제 상담 이용 수준이 높아 상담 프로그램 확대 또는 상담 인력 보완 검토; 학교폭력 피해 응답률 기반 위험 점수가 높아 학교폭력 관련 상담지원 강화 검토</t>
+          <t>대규모 학교로 상담수요 규모가 커 상담 인력 보강 검토</t>
         </is>
       </c>
       <c r="T109" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.419)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.381로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 학교폭력 위험 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.432)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.368로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>480041905</t>
+          <t>480041931</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>동원고등학교</t>
+          <t>창원대암고등학교</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -9611,7 +9611,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>통영시</t>
+          <t>창원시</t>
         </is>
       </c>
       <c r="E110" t="n">
@@ -9627,19 +9627,19 @@
         <v>1</v>
       </c>
       <c r="I110" t="n">
-        <v>0.184001935767832</v>
+        <v>0.2152890107824633</v>
       </c>
       <c r="J110" t="n">
-        <v>0.07175893199765718</v>
+        <v>0.05105071094104519</v>
       </c>
       <c r="K110" t="n">
         <v>0.7999999999999999</v>
       </c>
       <c r="L110" t="n">
-        <v>0.4185869559218298</v>
+        <v>0.4221132405745028</v>
       </c>
       <c r="M110" t="n">
-        <v>-0.3814130440781701</v>
+        <v>-0.3778867594254972</v>
       </c>
       <c r="N110" t="inlineStr">
         <is>
@@ -9673,19 +9673,19 @@
       </c>
       <c r="T110" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.419)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.381로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.422)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.378로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>480041690</t>
+          <t>480041537</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>마산중앙고등학교</t>
+          <t>하동고등학교</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -9695,7 +9695,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>창원시</t>
+          <t>하동군</t>
         </is>
       </c>
       <c r="E111" t="n">
@@ -9708,22 +9708,22 @@
         <v>1</v>
       </c>
       <c r="H111" t="n">
-        <v>0.6</v>
+        <v>0.3333</v>
       </c>
       <c r="I111" t="n">
-        <v>0.1751204810202206</v>
+        <v>0.4069727319013836</v>
       </c>
       <c r="J111" t="n">
-        <v>0.07802711107010211</v>
+        <v>0.1246313559557017</v>
       </c>
       <c r="K111" t="n">
         <v>0.6666666666666666</v>
       </c>
       <c r="L111" t="n">
-        <v>0.2843825306967742</v>
+        <v>0.2883013626190284</v>
       </c>
       <c r="M111" t="n">
-        <v>-0.3822841359698924</v>
+        <v>-0.3783653040476382</v>
       </c>
       <c r="N111" t="inlineStr">
         <is>
@@ -9752,24 +9752,24 @@
       </c>
       <c r="S111" t="inlineStr">
         <is>
-          <t>전문상담교사 배치 또는 순회상담교사 연계 검토</t>
+          <t>전문상담교사 배치 또는 순회상담교사 연계 검토; 실제 상담 이용 수준이 높아 상담 프로그램 확대 또는 상담 인력 보완 검토; 학교폭력 피해 응답률 기반 위험 점수가 높아 학교폭력 관련 상담지원 강화 검토</t>
         </is>
       </c>
       <c r="T111" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.284)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.382로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.288)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.378로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수, 학교폭력 위험 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>480041474</t>
+          <t>480041905</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>창원봉림고등학교</t>
+          <t>동원고등학교</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -9779,7 +9779,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>창원시</t>
+          <t>통영시</t>
         </is>
       </c>
       <c r="E112" t="n">
@@ -9795,19 +9795,19 @@
         <v>1</v>
       </c>
       <c r="I112" t="n">
-        <v>0.1574696928224008</v>
+        <v>0.184001935767832</v>
       </c>
       <c r="J112" t="n">
-        <v>0.08279367971131277</v>
+        <v>0.07175893199765718</v>
       </c>
       <c r="K112" t="n">
         <v>0.7999999999999999</v>
       </c>
       <c r="L112" t="n">
-        <v>0.4134211241779045</v>
+        <v>0.4185869559218298</v>
       </c>
       <c r="M112" t="n">
-        <v>-0.3865788758220954</v>
+        <v>-0.3814130440781701</v>
       </c>
       <c r="N112" t="inlineStr">
         <is>
@@ -9841,19 +9841,19 @@
       </c>
       <c r="T112" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.413)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.387로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.419)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.381로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>480041537</t>
+          <t>480041474</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>하동고등학교</t>
+          <t>창원봉림고등학교</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -9863,11 +9863,11 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>하동군</t>
+          <t>창원시</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="F113" t="n">
         <v>1</v>
@@ -9876,22 +9876,22 @@
         <v>1</v>
       </c>
       <c r="H113" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="I113" t="n">
-        <v>0.4069727319013836</v>
+        <v>0.1574696928224008</v>
       </c>
       <c r="J113" t="n">
-        <v>0.1246313559557017</v>
+        <v>0.08279367971131277</v>
       </c>
       <c r="K113" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7999999999999999</v>
       </c>
       <c r="L113" t="n">
-        <v>0.2772013626190284</v>
+        <v>0.4134211241779045</v>
       </c>
       <c r="M113" t="n">
-        <v>-0.3894653040476382</v>
+        <v>-0.3865788758220954</v>
       </c>
       <c r="N113" t="inlineStr">
         <is>
@@ -9905,27 +9905,27 @@
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>수요 낮음</t>
+          <t>수요 보통</t>
         </is>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>D. 수요낮음-공급높음</t>
+          <t>B. 수요높음-공급높음</t>
         </is>
       </c>
       <c r="R113" t="inlineStr">
         <is>
-          <t>현 수준 유지 또는 거점학교 활용</t>
+          <t>고수요 학교 모니터링 및 프로그램 강화</t>
         </is>
       </c>
       <c r="S113" t="inlineStr">
         <is>
-          <t>전문상담교사 배치 또는 순회상담교사 연계 검토; 실제 상담 이용 수준이 높아 상담 프로그램 확대 또는 상담 인력 보완 검토; 학교폭력 피해 응답률 기반 위험 점수가 높아 학교폭력 관련 상담지원 강화 검토</t>
+          <t>대규모 학교로 상담수요 규모가 커 상담 인력 보강 검토</t>
         </is>
       </c>
       <c r="T113" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.277)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.389로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수, 학교폭력 위험 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.413)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.387로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
@@ -10100,12 +10100,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>480041738</t>
+          <t>480041580</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>삼현여자고등학교</t>
+          <t>합천고등학교</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -10115,11 +10115,11 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>진주시</t>
+          <t>합천군</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="F116" t="n">
         <v>1</v>
@@ -10128,22 +10128,22 @@
         <v>1</v>
       </c>
       <c r="H116" t="n">
-        <v>1</v>
+        <v>0.3333</v>
       </c>
       <c r="I116" t="n">
-        <v>0.1617593889078537</v>
+        <v>0.4471977650045322</v>
       </c>
       <c r="J116" t="n">
-        <v>0.05266445430851617</v>
+        <v>0.03428571428571429</v>
       </c>
       <c r="K116" t="n">
-        <v>0.7999999999999999</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="L116" t="n">
-        <v>0.40480794773879</v>
+        <v>0.2715944930967488</v>
       </c>
       <c r="M116" t="n">
-        <v>-0.39519205226121</v>
+        <v>-0.3950721735699178</v>
       </c>
       <c r="N116" t="inlineStr">
         <is>
@@ -10157,39 +10157,39 @@
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>수요 보통</t>
+          <t>수요 낮음</t>
         </is>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
-          <t>B. 수요높음-공급높음</t>
+          <t>D. 수요낮음-공급높음</t>
         </is>
       </c>
       <c r="R116" t="inlineStr">
         <is>
-          <t>고수요 학교 모니터링 및 프로그램 강화</t>
+          <t>현 수준 유지 또는 거점학교 활용</t>
         </is>
       </c>
       <c r="S116" t="inlineStr">
         <is>
-          <t>대규모 학교로 상담수요 규모가 커 상담 인력 보강 검토</t>
+          <t>전문상담교사 배치 또는 순회상담교사 연계 검토; 실제 상담 이용 수준이 높아 상담 프로그램 확대 또는 상담 인력 보완 검토</t>
         </is>
       </c>
       <c r="T116" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.405)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.395로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.272)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.395로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>480041636</t>
+          <t>480041738</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>경해여자고등학교</t>
+          <t>삼현여자고등학교</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -10215,19 +10215,19 @@
         <v>1</v>
       </c>
       <c r="I117" t="n">
-        <v>0.1883641448245586</v>
+        <v>0.1617593889078537</v>
       </c>
       <c r="J117" t="n">
-        <v>0.02197802197802198</v>
+        <v>0.05266445430851617</v>
       </c>
       <c r="K117" t="n">
         <v>0.7999999999999999</v>
       </c>
       <c r="L117" t="n">
-        <v>0.4034473889341935</v>
+        <v>0.40480794773879</v>
       </c>
       <c r="M117" t="n">
-        <v>-0.3965526110658064</v>
+        <v>-0.39519205226121</v>
       </c>
       <c r="N117" t="inlineStr">
         <is>
@@ -10261,19 +10261,19 @@
       </c>
       <c r="T117" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.403)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.397로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.405)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.395로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>480041846</t>
+          <t>480041636</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>진주동명고등학교</t>
+          <t>경해여자고등학교</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -10299,19 +10299,19 @@
         <v>1</v>
       </c>
       <c r="I118" t="n">
-        <v>0.0765532478720137</v>
+        <v>0.1883641448245586</v>
       </c>
       <c r="J118" t="n">
-        <v>0.1084173804918486</v>
+        <v>0.02197802197802198</v>
       </c>
       <c r="K118" t="n">
         <v>0.7999999999999999</v>
       </c>
       <c r="L118" t="n">
-        <v>0.3949902094546208</v>
+        <v>0.4034473889341935</v>
       </c>
       <c r="M118" t="n">
-        <v>-0.4050097905453791</v>
+        <v>-0.3965526110658064</v>
       </c>
       <c r="N118" t="inlineStr">
         <is>
@@ -10345,19 +10345,19 @@
       </c>
       <c r="T118" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.395)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.405로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.403)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.397로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>480041580</t>
+          <t>480041846</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>합천고등학교</t>
+          <t>진주동명고등학교</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -10367,11 +10367,11 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>합천군</t>
+          <t>진주시</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="F119" t="n">
         <v>1</v>
@@ -10380,22 +10380,22 @@
         <v>1</v>
       </c>
       <c r="H119" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="I119" t="n">
-        <v>0.4471977650045322</v>
+        <v>0.0765532478720137</v>
       </c>
       <c r="J119" t="n">
-        <v>0.03428571428571429</v>
+        <v>0.1084173804918486</v>
       </c>
       <c r="K119" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7999999999999999</v>
       </c>
       <c r="L119" t="n">
-        <v>0.2604944930967488</v>
+        <v>0.3949902094546208</v>
       </c>
       <c r="M119" t="n">
-        <v>-0.4061721735699178</v>
+        <v>-0.4050097905453791</v>
       </c>
       <c r="N119" t="inlineStr">
         <is>
@@ -10409,39 +10409,39 @@
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>수요 낮음</t>
+          <t>수요 보통</t>
         </is>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>D. 수요낮음-공급높음</t>
+          <t>B. 수요높음-공급높음</t>
         </is>
       </c>
       <c r="R119" t="inlineStr">
         <is>
-          <t>현 수준 유지 또는 거점학교 활용</t>
+          <t>고수요 학교 모니터링 및 프로그램 강화</t>
         </is>
       </c>
       <c r="S119" t="inlineStr">
         <is>
-          <t>전문상담교사 배치 또는 순회상담교사 연계 검토; 실제 상담 이용 수준이 높아 상담 프로그램 확대 또는 상담 인력 보완 검토</t>
+          <t>대규모 학교로 상담수요 규모가 커 상담 인력 보강 검토</t>
         </is>
       </c>
       <c r="T119" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.260)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.406로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.395)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.405로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>480041882</t>
+          <t>480041900</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>창원고등학교</t>
+          <t>철성고등학교</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -10451,11 +10451,11 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>창원시</t>
+          <t>고성군</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="F120" t="n">
         <v>1</v>
@@ -10464,22 +10464,22 @@
         <v>1</v>
       </c>
       <c r="H120" t="n">
-        <v>1</v>
+        <v>0.6667</v>
       </c>
       <c r="I120" t="n">
-        <v>0.06255106816287991</v>
+        <v>0.1154682386344549</v>
       </c>
       <c r="J120" t="n">
-        <v>0.06535548537331762</v>
+        <v>0</v>
       </c>
       <c r="K120" t="n">
-        <v>0.7999999999999999</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="L120" t="n">
-        <v>0.3759688511787325</v>
+        <v>0.2607227462114849</v>
       </c>
       <c r="M120" t="n">
-        <v>-0.4240311488212674</v>
+        <v>-0.4059439204551817</v>
       </c>
       <c r="N120" t="inlineStr">
         <is>
@@ -10493,39 +10493,39 @@
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>수요 보통</t>
+          <t>수요 낮음</t>
         </is>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>B. 수요높음-공급높음</t>
+          <t>D. 수요낮음-공급높음</t>
         </is>
       </c>
       <c r="R120" t="inlineStr">
         <is>
-          <t>고수요 학교 모니터링 및 프로그램 강화</t>
+          <t>현 수준 유지 또는 거점학교 활용</t>
         </is>
       </c>
       <c r="S120" t="inlineStr">
         <is>
-          <t>대규모 학교로 상담수요 규모가 커 상담 인력 보강 검토</t>
+          <t>전문상담교사 배치 또는 순회상담교사 연계 검토</t>
         </is>
       </c>
       <c r="T120" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.376)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.424로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.261)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.406로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>480041900</t>
+          <t>480041648</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>철성고등학교</t>
+          <t>남지고등학교</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -10535,35 +10535,35 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>고성군</t>
+          <t>창녕군</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="F121" t="n">
         <v>1</v>
       </c>
       <c r="G121" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="H121" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="I121" t="n">
-        <v>0.1154682386344549</v>
+        <v>0.0329226182635174</v>
       </c>
       <c r="J121" t="n">
-        <v>0</v>
+        <v>0.139295825342337</v>
       </c>
       <c r="K121" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="L121" t="n">
-        <v>0.2384894128781516</v>
+        <v>0.2796394812019514</v>
       </c>
       <c r="M121" t="n">
-        <v>-0.428177253788515</v>
+        <v>-0.4203605187980486</v>
       </c>
       <c r="N121" t="inlineStr">
         <is>
@@ -10592,24 +10592,24 @@
       </c>
       <c r="S121" t="inlineStr">
         <is>
-          <t>전문상담교사 배치 또는 순회상담교사 연계 검토</t>
+          <t>Wee센터 접근성이 낮아 이동형 상담, 온라인 상담, 권역별 연계 강화 검토; 학교폭력 피해 응답률 기반 위험 점수가 높아 학교폭력 관련 상담지원 강화 검토</t>
         </is>
       </c>
       <c r="T121" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.238)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.428로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.700)가 상담수요지수(CDI=0.280)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.420로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 Wee센터 접근성 점수, 학교폭력 위험 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>480041648</t>
+          <t>480041882</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>남지고등학교</t>
+          <t>창원고등학교</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -10619,35 +10619,35 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>창녕군</t>
+          <t>창원시</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="F122" t="n">
         <v>1</v>
       </c>
       <c r="G122" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="H122" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="I122" t="n">
-        <v>0.0329226182635174</v>
+        <v>0.06255106816287991</v>
       </c>
       <c r="J122" t="n">
-        <v>0.139295825342337</v>
+        <v>0.06535548537331762</v>
       </c>
       <c r="K122" t="n">
-        <v>0.7000000000000001</v>
+        <v>0.7999999999999999</v>
       </c>
       <c r="L122" t="n">
-        <v>0.2574061478686181</v>
+        <v>0.3759688511787325</v>
       </c>
       <c r="M122" t="n">
-        <v>-0.442593852131382</v>
+        <v>-0.4240311488212674</v>
       </c>
       <c r="N122" t="inlineStr">
         <is>
@@ -10661,7 +10661,7 @@
       </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>수요 낮음</t>
+          <t>수요 보통</t>
         </is>
       </c>
       <c r="Q122" t="inlineStr">
@@ -10676,24 +10676,24 @@
       </c>
       <c r="S122" t="inlineStr">
         <is>
-          <t>Wee센터 접근성이 낮아 이동형 상담, 온라인 상담, 권역별 연계 강화 검토; 학교폭력 피해 응답률 기반 위험 점수가 높아 학교폭력 관련 상담지원 강화 검토</t>
+          <t>대규모 학교로 상담수요 규모가 커 상담 인력 보강 검토</t>
         </is>
       </c>
       <c r="T122" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.700)가 상담수요지수(CDI=0.257)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.443로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 Wee센터 접근성 점수, 학교폭력 위험 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.376)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.424로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>480041001</t>
+          <t>480041608</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>경상고등학교</t>
+          <t>대성일고등학교</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -10703,11 +10703,11 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>창원시</t>
+          <t>거창군</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="F123" t="n">
         <v>1</v>
@@ -10716,22 +10716,22 @@
         <v>1</v>
       </c>
       <c r="H123" t="n">
-        <v>1</v>
+        <v>0.6667</v>
       </c>
       <c r="I123" t="n">
-        <v>0.0585764310226926</v>
+        <v>0.4817851398830783</v>
       </c>
       <c r="J123" t="n">
-        <v>0</v>
+        <v>0.2339320004518243</v>
       </c>
       <c r="K123" t="n">
-        <v>0.7999999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="L123" t="n">
-        <v>0.3528588103408976</v>
+        <v>0.4608057134449675</v>
       </c>
       <c r="M123" t="n">
-        <v>-0.4471411896591023</v>
+        <v>-0.4391942865550325</v>
       </c>
       <c r="N123" t="inlineStr">
         <is>
@@ -10740,7 +10740,7 @@
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>공급 양호</t>
+          <t>공급 높음</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
@@ -10750,34 +10750,34 @@
       </c>
       <c r="Q123" t="inlineStr">
         <is>
-          <t>D. 수요낮음-공급높음</t>
+          <t>B. 수요높음-공급높음</t>
         </is>
       </c>
       <c r="R123" t="inlineStr">
         <is>
-          <t>현 수준 유지 또는 거점학교 활용</t>
+          <t>고수요 학교 모니터링 및 프로그램 강화</t>
         </is>
       </c>
       <c r="S123" t="inlineStr">
         <is>
-          <t>대규모 학교로 상담수요 규모가 커 상담 인력 보강 검토</t>
+          <t>실제 상담 이용 수준이 높아 상담 프로그램 확대 또는 상담 인력 보완 검토; 학교폭력 피해 응답률 기반 위험 점수가 높아 학교폭력 관련 상담지원 강화 검토</t>
         </is>
       </c>
       <c r="T123" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.353)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.447로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.900)가 상담수요지수(CDI=0.461)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.439로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 학교폭력 위험 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>480041608</t>
+          <t>480041001</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>대성일고등학교</t>
+          <t>경상고등학교</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -10787,11 +10787,11 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>거창군</t>
+          <t>창원시</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="F124" t="n">
         <v>1</v>
@@ -10800,22 +10800,22 @@
         <v>1</v>
       </c>
       <c r="H124" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="I124" t="n">
-        <v>0.4817851398830783</v>
+        <v>0.0585764310226926</v>
       </c>
       <c r="J124" t="n">
-        <v>0.2339320004518243</v>
+        <v>0</v>
       </c>
       <c r="K124" t="n">
-        <v>0.9</v>
+        <v>0.7999999999999999</v>
       </c>
       <c r="L124" t="n">
-        <v>0.4385723801116342</v>
+        <v>0.3528588103408976</v>
       </c>
       <c r="M124" t="n">
-        <v>-0.4614276198883658</v>
+        <v>-0.4471411896591023</v>
       </c>
       <c r="N124" t="inlineStr">
         <is>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>공급 높음</t>
+          <t>공급 양호</t>
         </is>
       </c>
       <c r="P124" t="inlineStr">
@@ -10834,22 +10834,22 @@
       </c>
       <c r="Q124" t="inlineStr">
         <is>
-          <t>B. 수요높음-공급높음</t>
+          <t>D. 수요낮음-공급높음</t>
         </is>
       </c>
       <c r="R124" t="inlineStr">
         <is>
-          <t>고수요 학교 모니터링 및 프로그램 강화</t>
+          <t>현 수준 유지 또는 거점학교 활용</t>
         </is>
       </c>
       <c r="S124" t="inlineStr">
         <is>
-          <t>실제 상담 이용 수준이 높아 상담 프로그램 확대 또는 상담 인력 보완 검토; 학교폭력 피해 응답률 기반 위험 점수가 높아 학교폭력 관련 상담지원 강화 검토</t>
+          <t>대규모 학교로 상담수요 규모가 커 상담 인력 보강 검토</t>
         </is>
       </c>
       <c r="T124" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.900)가 상담수요지수(CDI=0.439)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.461로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 학교폭력 위험 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.353)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.447로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
@@ -10884,7 +10884,7 @@
         <v>1</v>
       </c>
       <c r="H125" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="I125" t="n">
         <v>0.2559463474428509</v>
@@ -10896,10 +10896,10 @@
         <v>0.6666666666666666</v>
       </c>
       <c r="L125" t="n">
-        <v>0.1999139892936024</v>
+        <v>0.2110139892936024</v>
       </c>
       <c r="M125" t="n">
-        <v>-0.4667526773730643</v>
+        <v>-0.4556526773730643</v>
       </c>
       <c r="N125" t="inlineStr">
         <is>
@@ -10933,19 +10933,19 @@
       </c>
       <c r="T125" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.200)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.467로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.211)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.456로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>480041864</t>
+          <t>480041245</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>창녕고등학교</t>
+          <t>마산가포고등학교</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -10955,35 +10955,35 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>창녕군</t>
+          <t>창원시</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="F126" t="n">
         <v>1</v>
       </c>
       <c r="G126" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="H126" t="n">
-        <v>0.3</v>
+        <v>0.6667</v>
       </c>
       <c r="I126" t="n">
-        <v>0.2361623444441073</v>
+        <v>0.2674391673483604</v>
       </c>
       <c r="J126" t="n">
-        <v>0.04379562043795621</v>
+        <v>0.09115131768568528</v>
       </c>
       <c r="K126" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7999999999999999</v>
       </c>
       <c r="L126" t="n">
-        <v>0.1933193216273545</v>
+        <v>0.3417634950113486</v>
       </c>
       <c r="M126" t="n">
-        <v>-0.4733473450393121</v>
+        <v>-0.4582365049886513</v>
       </c>
       <c r="N126" t="inlineStr">
         <is>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>수요 낮음</t>
+          <t>수요 보통</t>
         </is>
       </c>
       <c r="Q126" t="inlineStr">
@@ -11012,24 +11012,24 @@
       </c>
       <c r="S126" t="inlineStr">
         <is>
-          <t>전문상담교사 배치 또는 순회상담교사 연계 검토</t>
+          <t>현 수준 유지 및 정기 모니터링</t>
         </is>
       </c>
       <c r="T126" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.193)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.473로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.342)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.458로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>480041245</t>
+          <t>480041864</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>마산가포고등학교</t>
+          <t>창녕고등학교</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -11039,35 +11039,35 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>창원시</t>
+          <t>창녕군</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="F127" t="n">
         <v>1</v>
       </c>
       <c r="G127" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="H127" t="n">
-        <v>0.6</v>
+        <v>0.3333</v>
       </c>
       <c r="I127" t="n">
-        <v>0.2674391673483604</v>
+        <v>0.2361623444441073</v>
       </c>
       <c r="J127" t="n">
-        <v>0.09115131768568528</v>
+        <v>0.04379562043795621</v>
       </c>
       <c r="K127" t="n">
-        <v>0.7999999999999999</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="L127" t="n">
-        <v>0.3195301616780152</v>
+        <v>0.2044193216273545</v>
       </c>
       <c r="M127" t="n">
-        <v>-0.4804698383219848</v>
+        <v>-0.4622473450393121</v>
       </c>
       <c r="N127" t="inlineStr">
         <is>
@@ -11081,7 +11081,7 @@
       </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>수요 보통</t>
+          <t>수요 낮음</t>
         </is>
       </c>
       <c r="Q127" t="inlineStr">
@@ -11096,12 +11096,12 @@
       </c>
       <c r="S127" t="inlineStr">
         <is>
-          <t>현 수준 유지 및 정기 모니터링</t>
+          <t>전문상담교사 배치 또는 순회상담교사 연계 검토</t>
         </is>
       </c>
       <c r="T127" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.320)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.480로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.204)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.462로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
         <v>0.4</v>
       </c>
       <c r="H128" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="I128" t="n">
         <v>0.5170066198206746</v>
@@ -11148,10 +11148,10 @@
         <v>0.7999999999999999</v>
       </c>
       <c r="L128" t="n">
-        <v>0.3166982850382641</v>
+        <v>0.3277982850382641</v>
       </c>
       <c r="M128" t="n">
-        <v>-0.4833017149617359</v>
+        <v>-0.4722017149617359</v>
       </c>
       <c r="N128" t="inlineStr">
         <is>
@@ -11185,7 +11185,7 @@
       </c>
       <c r="T128" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.317)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.483로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 Wee센터 접근성 점수, 학교폭력 위험 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.328)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.472로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 Wee센터 접근성 점수, 학교폭력 위험 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
@@ -11220,7 +11220,7 @@
         <v>1</v>
       </c>
       <c r="H129" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="I129" t="n">
         <v>0.4936783384019001</v>
@@ -11232,10 +11232,10 @@
         <v>0.9</v>
       </c>
       <c r="L129" t="n">
-        <v>0.3994221774928415</v>
+        <v>0.4216555108261748</v>
       </c>
       <c r="M129" t="n">
-        <v>-0.5005778225071585</v>
+        <v>-0.4783444891738252</v>
       </c>
       <c r="N129" t="inlineStr">
         <is>
@@ -11269,19 +11269,19 @@
       </c>
       <c r="T129" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.900)가 상담수요지수(CDI=0.399)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.501로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.900)가 상담수요지수(CDI=0.422)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.478로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>480041901</t>
+          <t>480041633</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>충렬여자고등학교</t>
+          <t>고성고등학교</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -11291,7 +11291,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>통영시</t>
+          <t>고성군</t>
         </is>
       </c>
       <c r="E130" t="n">
@@ -11301,25 +11301,25 @@
         <v>1</v>
       </c>
       <c r="G130" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="H130" t="n">
-        <v>1</v>
+        <v>0.6667</v>
       </c>
       <c r="I130" t="n">
-        <v>0.1345182690610425</v>
+        <v>0.2611738807004353</v>
       </c>
       <c r="J130" t="n">
-        <v>0.03025292194370326</v>
+        <v>0</v>
       </c>
       <c r="K130" t="n">
-        <v>0.9</v>
+        <v>0.7999999999999999</v>
       </c>
       <c r="L130" t="n">
-        <v>0.3882570636682486</v>
+        <v>0.3092912935668117</v>
       </c>
       <c r="M130" t="n">
-        <v>-0.5117429363317514</v>
+        <v>-0.4907087064331883</v>
       </c>
       <c r="N130" t="inlineStr">
         <is>
@@ -11328,7 +11328,7 @@
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>공급 높음</t>
+          <t>공급 양호</t>
         </is>
       </c>
       <c r="P130" t="inlineStr">
@@ -11338,34 +11338,34 @@
       </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>B. 수요높음-공급높음</t>
+          <t>D. 수요낮음-공급높음</t>
         </is>
       </c>
       <c r="R130" t="inlineStr">
         <is>
-          <t>고수요 학교 모니터링 및 프로그램 강화</t>
+          <t>현 수준 유지 또는 거점학교 활용</t>
         </is>
       </c>
       <c r="S130" t="inlineStr">
         <is>
-          <t>대규모 학교로 상담수요 규모가 커 상담 인력 보강 검토</t>
+          <t>현 수준 유지 및 정기 모니터링</t>
         </is>
       </c>
       <c r="T130" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.900)가 상담수요지수(CDI=0.388)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.512로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.309)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.491로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>480041633</t>
+          <t>480041901</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>고성고등학교</t>
+          <t>충렬여자고등학교</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -11375,7 +11375,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>고성군</t>
+          <t>통영시</t>
         </is>
       </c>
       <c r="E131" t="n">
@@ -11385,25 +11385,25 @@
         <v>1</v>
       </c>
       <c r="G131" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="H131" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="I131" t="n">
-        <v>0.2611738807004353</v>
+        <v>0.1345182690610425</v>
       </c>
       <c r="J131" t="n">
-        <v>0</v>
+        <v>0.03025292194370326</v>
       </c>
       <c r="K131" t="n">
-        <v>0.7999999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="L131" t="n">
-        <v>0.2870579602334784</v>
+        <v>0.3882570636682486</v>
       </c>
       <c r="M131" t="n">
-        <v>-0.5129420397665215</v>
+        <v>-0.5117429363317514</v>
       </c>
       <c r="N131" t="inlineStr">
         <is>
@@ -11412,32 +11412,32 @@
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>공급 양호</t>
+          <t>공급 높음</t>
         </is>
       </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>수요 낮음</t>
+          <t>수요 보통</t>
         </is>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>D. 수요낮음-공급높음</t>
+          <t>B. 수요높음-공급높음</t>
         </is>
       </c>
       <c r="R131" t="inlineStr">
         <is>
-          <t>현 수준 유지 또는 거점학교 활용</t>
+          <t>고수요 학교 모니터링 및 프로그램 강화</t>
         </is>
       </c>
       <c r="S131" t="inlineStr">
         <is>
-          <t>현 수준 유지 및 정기 모니터링</t>
+          <t>대규모 학교로 상담수요 규모가 커 상담 인력 보강 검토</t>
         </is>
       </c>
       <c r="T131" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.287)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.513로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.900)가 상담수요지수(CDI=0.388)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.512로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
@@ -11472,7 +11472,7 @@
         <v>1</v>
       </c>
       <c r="H132" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="I132" t="n">
         <v>0.3981295677618628</v>
@@ -11484,10 +11484,10 @@
         <v>0.9</v>
       </c>
       <c r="L132" t="n">
-        <v>0.3561690715057095</v>
+        <v>0.3784024048390429</v>
       </c>
       <c r="M132" t="n">
-        <v>-0.5438309284942906</v>
+        <v>-0.5215975951609571</v>
       </c>
       <c r="N132" t="inlineStr">
         <is>
@@ -11521,19 +11521,19 @@
       </c>
       <c r="T132" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.900)가 상담수요지수(CDI=0.356)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.544로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.900)가 상담수요지수(CDI=0.378)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.522로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>480041331</t>
+          <t>480041928</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>안의고등학교</t>
+          <t>명덕고등학교</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -11543,35 +11543,35 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>함양군</t>
+          <t>함안군</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="F133" t="n">
         <v>1</v>
       </c>
       <c r="G133" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="H133" t="n">
-        <v>0.3</v>
+        <v>0.6667</v>
       </c>
       <c r="I133" t="n">
-        <v>0.454263085399187</v>
+        <v>0.3808201961902997</v>
       </c>
       <c r="J133" t="n">
-        <v>0</v>
+        <v>0.05882352941176471</v>
       </c>
       <c r="K133" t="n">
-        <v>0.7999999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="L133" t="n">
-        <v>0.2514210284663956</v>
+        <v>0.3687812418673548</v>
       </c>
       <c r="M133" t="n">
-        <v>-0.5485789715336044</v>
+        <v>-0.5312187581326453</v>
       </c>
       <c r="N133" t="inlineStr">
         <is>
@@ -11580,12 +11580,12 @@
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>공급 양호</t>
+          <t>공급 높음</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>수요 낮음</t>
+          <t>수요 보통</t>
         </is>
       </c>
       <c r="Q133" t="inlineStr">
@@ -11600,24 +11600,24 @@
       </c>
       <c r="S133" t="inlineStr">
         <is>
-          <t>Wee센터 접근성이 낮아 이동형 상담, 온라인 상담, 권역별 연계 강화 검토; 실제 상담 이용 수준이 높아 상담 프로그램 확대 또는 상담 인력 보완 검토</t>
+          <t>현 수준 유지 및 정기 모니터링</t>
         </is>
       </c>
       <c r="T133" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.251)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.549로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 Wee센터 접근성 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.900)가 상담수요지수(CDI=0.369)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.531로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>480041928</t>
+          <t>480041331</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>명덕고등학교</t>
+          <t>안의고등학교</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -11627,35 +11627,35 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>함안군</t>
+          <t>함양군</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="F134" t="n">
         <v>1</v>
       </c>
       <c r="G134" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="H134" t="n">
-        <v>0.6</v>
+        <v>0.3333</v>
       </c>
       <c r="I134" t="n">
-        <v>0.3808201961902997</v>
+        <v>0.454263085399187</v>
       </c>
       <c r="J134" t="n">
-        <v>0.05882352941176471</v>
+        <v>0</v>
       </c>
       <c r="K134" t="n">
-        <v>0.9</v>
+        <v>0.7999999999999999</v>
       </c>
       <c r="L134" t="n">
-        <v>0.3465479085340215</v>
+        <v>0.2625210284663957</v>
       </c>
       <c r="M134" t="n">
-        <v>-0.5534520914659785</v>
+        <v>-0.5374789715336042</v>
       </c>
       <c r="N134" t="inlineStr">
         <is>
@@ -11664,12 +11664,12 @@
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>공급 높음</t>
+          <t>공급 양호</t>
         </is>
       </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>수요 보통</t>
+          <t>수요 낮음</t>
         </is>
       </c>
       <c r="Q134" t="inlineStr">
@@ -11684,12 +11684,12 @@
       </c>
       <c r="S134" t="inlineStr">
         <is>
-          <t>현 수준 유지 및 정기 모니터링</t>
+          <t>Wee센터 접근성이 낮아 이동형 상담, 온라인 상담, 권역별 연계 강화 검토; 실제 상담 이용 수준이 높아 상담 프로그램 확대 또는 상담 인력 보완 검토</t>
         </is>
       </c>
       <c r="T134" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.900)가 상담수요지수(CDI=0.347)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.553로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.263)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.537로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 Wee센터 접근성 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
@@ -11724,7 +11724,7 @@
         <v>1</v>
       </c>
       <c r="H135" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="I135" t="n">
         <v>0.3240687900487338</v>
@@ -11736,10 +11736,10 @@
         <v>0.9</v>
       </c>
       <c r="L135" t="n">
-        <v>0.331761994710056</v>
+        <v>0.3539953280433893</v>
       </c>
       <c r="M135" t="n">
-        <v>-0.5682380052899441</v>
+        <v>-0.5460046719566107</v>
       </c>
       <c r="N135" t="inlineStr">
         <is>
@@ -11773,7 +11773,7 @@
       </c>
       <c r="T135" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.900)가 상담수요지수(CDI=0.332)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.568로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.900)가 상담수요지수(CDI=0.354)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.546로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
@@ -11808,7 +11808,7 @@
         <v>1</v>
       </c>
       <c r="H136" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="I136" t="n">
         <v>0.2718666795525124</v>
@@ -11820,10 +11820,10 @@
         <v>0.9</v>
       </c>
       <c r="L136" t="n">
-        <v>0.3271729027311277</v>
+        <v>0.349406236064461</v>
       </c>
       <c r="M136" t="n">
-        <v>-0.5728270972688723</v>
+        <v>-0.550593763935539</v>
       </c>
       <c r="N136" t="inlineStr">
         <is>
@@ -11857,7 +11857,7 @@
       </c>
       <c r="T136" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.900)가 상담수요지수(CDI=0.327)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.573로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.900)가 상담수요지수(CDI=0.349)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.551로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
@@ -11892,7 +11892,7 @@
         <v>1</v>
       </c>
       <c r="H137" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="I137" t="n">
         <v>0.2865279309795805</v>
@@ -11904,10 +11904,10 @@
         <v>0.9</v>
       </c>
       <c r="L137" t="n">
-        <v>0.3258272363934743</v>
+        <v>0.3480605697268076</v>
       </c>
       <c r="M137" t="n">
-        <v>-0.5741727636065257</v>
+        <v>-0.5519394302731924</v>
       </c>
       <c r="N137" t="inlineStr">
         <is>
@@ -11941,7 +11941,7 @@
       </c>
       <c r="T137" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.900)가 상담수요지수(CDI=0.326)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.574로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.900)가 상담수요지수(CDI=0.348)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.552로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
@@ -11976,7 +11976,7 @@
         <v>1</v>
       </c>
       <c r="H138" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="I138" t="n">
         <v>0.3595670410503039</v>
@@ -11988,10 +11988,10 @@
         <v>0.9</v>
       </c>
       <c r="L138" t="n">
-        <v>0.3198556803501013</v>
+        <v>0.3420890136834346</v>
       </c>
       <c r="M138" t="n">
-        <v>-0.5801443196498988</v>
+        <v>-0.5579109863165654</v>
       </c>
       <c r="N138" t="inlineStr">
         <is>
@@ -12025,7 +12025,7 @@
       </c>
       <c r="T138" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.900)가 상담수요지수(CDI=0.320)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.580로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.900)가 상담수요지수(CDI=0.342)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.558로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
@@ -12060,7 +12060,7 @@
         <v>1</v>
       </c>
       <c r="H139" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="I139" t="n">
         <v>0.2004335900090441</v>
@@ -12072,10 +12072,10 @@
         <v>0.9</v>
       </c>
       <c r="L139" t="n">
-        <v>0.2753218349675537</v>
+        <v>0.297555168300887</v>
       </c>
       <c r="M139" t="n">
-        <v>-0.6246781650324463</v>
+        <v>-0.602444831699113</v>
       </c>
       <c r="N139" t="inlineStr">
         <is>
@@ -12109,7 +12109,7 @@
       </c>
       <c r="T139" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.900)가 상담수요지수(CDI=0.275)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.625로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.900)가 상담수요지수(CDI=0.298)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.602로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
@@ -12144,7 +12144,7 @@
         <v>1</v>
       </c>
       <c r="H140" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="I140" t="n">
         <v>0.1478611366284428</v>
@@ -12156,10 +12156,10 @@
         <v>0.9</v>
       </c>
       <c r="L140" t="n">
-        <v>0.2729090927869087</v>
+        <v>0.2951424261202421</v>
       </c>
       <c r="M140" t="n">
-        <v>-0.6270909072130912</v>
+        <v>-0.6048575738797579</v>
       </c>
       <c r="N140" t="inlineStr">
         <is>
@@ -12193,7 +12193,7 @@
       </c>
       <c r="T140" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.900)가 상담수요지수(CDI=0.273)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.627로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.900)가 상담수요지수(CDI=0.295)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.605로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
@@ -12228,7 +12228,7 @@
         <v>0.7</v>
       </c>
       <c r="H141" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="I141" t="n">
         <v>0.4071925075669307</v>
@@ -12240,10 +12240,10 @@
         <v>0.9</v>
       </c>
       <c r="L141" t="n">
-        <v>0.2563493925566745</v>
+        <v>0.2674493925566745</v>
       </c>
       <c r="M141" t="n">
-        <v>-0.6436506074433255</v>
+        <v>-0.6325506074433256</v>
       </c>
       <c r="N141" t="inlineStr">
         <is>
@@ -12277,7 +12277,7 @@
       </c>
       <c r="T141" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.900)가 상담수요지수(CDI=0.256)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.644로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.900)가 상담수요지수(CDI=0.267)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.633로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
@@ -12312,7 +12312,7 @@
         <v>1</v>
       </c>
       <c r="H142" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="I142" t="n">
         <v>0.0255824556496562</v>
@@ -12324,10 +12324,10 @@
         <v>0.9</v>
       </c>
       <c r="L142" t="n">
-        <v>0.2388079746087166</v>
+        <v>0.2610413079420499</v>
       </c>
       <c r="M142" t="n">
-        <v>-0.6611920253912834</v>
+        <v>-0.6389586920579502</v>
       </c>
       <c r="N142" t="inlineStr">
         <is>
@@ -12361,7 +12361,7 @@
       </c>
       <c r="T142" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.900)가 상담수요지수(CDI=0.239)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.661로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.900)가 상담수요지수(CDI=0.261)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.639로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
@@ -12396,7 +12396,7 @@
         <v>1</v>
       </c>
       <c r="H143" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="I143" t="n">
         <v>0.1131027623352295</v>
@@ -12408,10 +12408,10 @@
         <v>0.9</v>
       </c>
       <c r="L143" t="n">
-        <v>0.2377009207784098</v>
+        <v>0.2599342541117431</v>
       </c>
       <c r="M143" t="n">
-        <v>-0.6622990792215903</v>
+        <v>-0.6400657458882569</v>
       </c>
       <c r="N143" t="inlineStr">
         <is>
@@ -12445,7 +12445,7 @@
       </c>
       <c r="T143" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.900)가 상담수요지수(CDI=0.238)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.662로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.900)가 상담수요지수(CDI=0.260)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.640로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
@@ -12480,7 +12480,7 @@
         <v>1</v>
       </c>
       <c r="H144" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="I144" t="n">
         <v>0.3982246984762633</v>
@@ -12492,10 +12492,10 @@
         <v>1</v>
       </c>
       <c r="L144" t="n">
-        <v>0.2527415661587544</v>
+        <v>0.2638415661587545</v>
       </c>
       <c r="M144" t="n">
-        <v>-0.7472584338412456</v>
+        <v>-0.7361584338412455</v>
       </c>
       <c r="N144" t="inlineStr">
         <is>
@@ -12529,7 +12529,7 @@
       </c>
       <c r="T144" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=1.000)가 상담수요지수(CDI=0.253)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.747로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=1.000)가 상담수요지수(CDI=0.264)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.736로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
@@ -12564,7 +12564,7 @@
         <v>1</v>
       </c>
       <c r="H145" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="I145" t="n">
         <v>0.3164180297242954</v>
@@ -12576,10 +12576,10 @@
         <v>1</v>
       </c>
       <c r="L145" t="n">
-        <v>0.2428185164219077</v>
+        <v>0.2539185164219077</v>
       </c>
       <c r="M145" t="n">
-        <v>-0.7571814835780923</v>
+        <v>-0.7460814835780922</v>
       </c>
       <c r="N145" t="inlineStr">
         <is>
@@ -12613,7 +12613,7 @@
       </c>
       <c r="T145" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=1.000)가 상담수요지수(CDI=0.243)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.757로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=1.000)가 상담수요지수(CDI=0.254)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.746로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
@@ -12648,7 +12648,7 @@
         <v>1</v>
       </c>
       <c r="H146" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="I146" t="n">
         <v>0.1976726557730393</v>
@@ -12660,10 +12660,10 @@
         <v>1</v>
       </c>
       <c r="L146" t="n">
-        <v>0.2045189238857184</v>
+        <v>0.2156189238857184</v>
       </c>
       <c r="M146" t="n">
-        <v>-0.7954810761142816</v>
+        <v>-0.7843810761142815</v>
       </c>
       <c r="N146" t="inlineStr">
         <is>
@@ -12697,7 +12697,7 @@
       </c>
       <c r="T146" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=1.000)가 상담수요지수(CDI=0.205)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.795로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 학교폭력 위험 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=1.000)가 상담수요지수(CDI=0.216)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.784로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 학교폭력 위험 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
@@ -12732,7 +12732,7 @@
         <v>1</v>
       </c>
       <c r="H147" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="I147" t="n">
         <v>0.2051374145411299</v>
@@ -12744,10 +12744,10 @@
         <v>1</v>
       </c>
       <c r="L147" t="n">
-        <v>0.1791899489911875</v>
+        <v>0.1902899489911875</v>
       </c>
       <c r="M147" t="n">
-        <v>-0.8208100510088125</v>
+        <v>-0.8097100510088124</v>
       </c>
       <c r="N147" t="inlineStr">
         <is>
@@ -12781,7 +12781,7 @@
       </c>
       <c r="T147" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=1.000)가 상담수요지수(CDI=0.179)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.821로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=1.000)가 상담수요지수(CDI=0.190)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.810로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
     </row>
@@ -12838,16 +12838,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C2" t="n">
-        <v>0.45</v>
+        <v>0.4614</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4549</v>
+        <v>0.4619</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0049</v>
+        <v>0.0005</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -12862,16 +12862,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7441</v>
+        <v>0.7407</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4504</v>
+        <v>0.4509</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.2937</v>
+        <v>-0.2898</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -12886,16 +12886,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C4" t="n">
-        <v>0.347</v>
+        <v>0.342</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2323</v>
+        <v>0.2531</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.1147</v>
+        <v>-0.089</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -12910,16 +12910,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7762</v>
+        <v>0.7821</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2939</v>
+        <v>0.3102</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.4823</v>
+        <v>-0.472</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -12970,7 +12970,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3">
@@ -12985,7 +12985,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4">
@@ -13030,7 +13030,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
@@ -13045,7 +13045,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -13297,10 +13297,10 @@
         <v>0.3833</v>
       </c>
       <c r="D2" t="n">
-        <v>0.22</v>
+        <v>0.2339</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.1633</v>
+        <v>-0.1494</v>
       </c>
       <c r="F2" t="n">
         <v>2</v>
@@ -13325,10 +13325,10 @@
         <v>0.5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3314</v>
+        <v>0.3462</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1686</v>
+        <v>-0.1538</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
@@ -13381,10 +13381,10 @@
         <v>0.5417</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3253</v>
+        <v>0.3447</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2164</v>
+        <v>-0.1969</v>
       </c>
       <c r="F5" t="n">
         <v>1</v>
@@ -13399,54 +13399,54 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>양산시</t>
+          <t>사천시</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6636</v>
+        <v>0.5722</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4471</v>
+        <v>0.3628</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2166</v>
+        <v>-0.2094</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
         <v>2</v>
       </c>
       <c r="H6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>김해시</t>
+          <t>양산시</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6667</v>
+        <v>0.6636</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4486</v>
+        <v>0.4491</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2181</v>
+        <v>-0.2146</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
         <v>4</v>
@@ -13455,29 +13455,29 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>사천시</t>
+          <t>김해시</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5722</v>
+        <v>0.6667</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3462</v>
+        <v>0.4512</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2261</v>
+        <v>-0.2155</v>
       </c>
       <c r="F8" t="n">
         <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -13493,10 +13493,10 @@
         <v>0.5667</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3145</v>
+        <v>0.3339</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2522</v>
+        <v>-0.2328</v>
       </c>
       <c r="F9" t="n">
         <v>1</v>
@@ -13521,16 +13521,16 @@
         <v>0.6667</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4002</v>
+        <v>0.4037</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.2664</v>
+        <v>-0.263</v>
       </c>
       <c r="F10" t="n">
         <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
         <v>2</v>
@@ -13539,57 +13539,57 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>창원시</t>
+          <t>밀양시</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6825</v>
+        <v>0.5833</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4039</v>
+        <v>0.3142</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.2786</v>
+        <v>-0.2692</v>
       </c>
       <c r="F11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>밀양시</t>
+          <t>창원시</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5833</v>
+        <v>0.6825</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2956</v>
+        <v>0.4106</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.2877</v>
+        <v>-0.2719</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -13605,10 +13605,10 @@
         <v>0.5266999999999999</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2317</v>
+        <v>0.2428</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.295</v>
+        <v>-0.2839</v>
       </c>
       <c r="F13" t="n">
         <v>1</v>
@@ -13661,10 +13661,10 @@
         <v>0.6</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2289</v>
+        <v>0.24</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.3711</v>
+        <v>-0.36</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -13689,10 +13689,10 @@
         <v>0.7111</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2759</v>
+        <v>0.2981</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.4352</v>
+        <v>-0.413</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -13717,10 +13717,10 @@
         <v>0.7167</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2512</v>
+        <v>0.266</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.4655</v>
+        <v>-0.4507</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -13745,10 +13745,10 @@
         <v>0.6667</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1693</v>
+        <v>0.1804</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.4974</v>
+        <v>-0.4863</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -13773,10 +13773,10 @@
         <v>0.8222</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2871</v>
+        <v>0.3075</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.5351</v>
+        <v>-0.5148</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
